--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1355,7 +1355,7 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1363,7 +1363,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P6" s="12" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="69" customHeight="1" s="19">
       <c r="A7" s="13" t="inlineStr">
@@ -1426,7 +1430,7 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1434,7 +1438,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P7" s="14" t="n"/>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55.2" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -1497,7 +1505,7 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1505,7 +1513,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P8" s="12" t="n"/>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="82.8" customHeight="1" s="19">
       <c r="A9" s="13" t="inlineStr">
@@ -1576,7 +1588,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P9" s="14" t="n"/>
+      <c r="P9" s="14" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc/PO) bloqueadas hasta que exista el desarrollo.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55.2" customHeight="1" s="19">
       <c r="A10" s="11" t="inlineStr">
@@ -1710,7 +1726,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1718,7 +1734,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P11" s="14" t="n"/>
+      <c r="P11" s="14" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="69" customHeight="1" s="19">
       <c r="A12" s="11" t="inlineStr">
@@ -1781,7 +1801,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -1789,7 +1809,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P12" s="12" t="n"/>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A13" s="13" t="inlineStr">
@@ -1860,7 +1884,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P13" s="14" t="n"/>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc) terminadas: publicar y abrir versión nueva desde el centro del plan (BD/219). Estado de la historia lo cierra Emilio.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -1931,7 +1959,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P14" s="12" t="n"/>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc/PO) bloqueadas hasta que exista el desarrollo.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55.2" customHeight="1" s="19">
       <c r="A15" s="13" t="inlineStr">
@@ -2004,7 +2036,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico adjunta. La galeria es HU-142.</t>
+          <t>Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P18" s="12" t="n"/>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc) terminadas sobre el calendario del plan y generar OT (BD/216, BD/220). La bandeja global es de Catalina.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2290,7 +2326,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P19" s="14" t="n"/>
+      <c r="P19" s="14" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc) bloqueadas hasta que exista el desarrollo.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="69" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -2424,7 +2464,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
@@ -2432,7 +2472,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P21" s="14" t="n"/>
+      <c r="P21" s="14" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="69" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -2574,7 +2618,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P23" s="14" t="n"/>
+      <c r="P23" s="14" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="69" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -2779,7 +2827,7 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -2787,7 +2835,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P26" s="12" t="n"/>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="82.8" customHeight="1" s="19">
       <c r="A27" s="13" t="inlineStr">
@@ -2858,7 +2910,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P27" s="14" t="n"/>
+      <c r="P27" s="14" t="inlineStr">
+        <is>
+          <t>Tareas de Bryan (pruebas/doc) bloqueadas hasta que exista el desarrollo.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55.2" customHeight="1" s="19">
       <c r="A28" s="11" t="inlineStr">
@@ -2992,7 +3048,7 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
@@ -3000,7 +3056,11 @@
           <t>Bryan Chávez</t>
         </is>
       </c>
-      <c r="P29" s="14" t="n"/>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="n"/>
@@ -3200,11 +3260,17 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>BD/212. Índice UX_PMA_CLIENTE_CODIGO confirmado; código PMA- automático vía Modulo_Codigo.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="41.4" customHeight="1" s="19">
       <c r="A7" s="11" t="inlineStr">
@@ -3242,10 +3308,12 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J7" s="12" t="n"/>
     </row>
     <row r="8" ht="41.4" customHeight="1" s="19">
@@ -3284,11 +3352,17 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="n"/>
-      <c r="J8" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>INS crea la versión 1 en BORRADOR en la misma transacción.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="41.4" customHeight="1" s="19">
       <c r="A9" s="11" t="inlineStr">
@@ -3326,10 +3400,12 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J9" s="12" t="n"/>
     </row>
     <row r="10" ht="41.4" customHeight="1" s="19">
@@ -3368,10 +3444,12 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J10" s="12" t="n"/>
     </row>
     <row r="11" ht="27.6" customHeight="1" s="19">
@@ -3410,10 +3488,12 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J11" s="12" t="n"/>
     </row>
     <row r="12" ht="27.6" customHeight="1" s="19">
@@ -3452,10 +3532,12 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" s="12" t="n"/>
     </row>
     <row r="13" ht="41.4" customHeight="1" s="19">
@@ -3494,11 +3576,17 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>Hecha en Default.master con pestañas (Ficha/Hitos/Equipos/Calendario/Versiones), no en RadWindow: el plan es el centro de operaciones (decisión del 12-09).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27.6" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -3536,10 +3624,12 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I14" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J14" s="12" t="n"/>
     </row>
     <row r="15" ht="27.6" customHeight="1" s="19">
@@ -3578,11 +3668,17 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>Menus + Menu_Funcion; cliente desde la sesión en el controlador; negativo con Cristián Muñoz (ámbito app) verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="27.6" customHeight="1" s="19">
       <c r="A16" s="11" t="inlineStr">
@@ -3746,11 +3842,17 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>BD/213. El código del hito es único DENTRO DE LA VERSIÓN (UX_PMH_VERSION_CODIGO), no del cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="41.4" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -3788,10 +3890,12 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I20" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J20" s="12" t="n"/>
     </row>
     <row r="21" ht="41.4" customHeight="1" s="19">
@@ -3830,11 +3934,17 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>INS recibe el plan y cuelga el hito a su borrador; rechaza si no hay borrador.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27.6" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -3872,10 +3982,12 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I22" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J22" s="12" t="n"/>
     </row>
     <row r="23" ht="41.4" customHeight="1" s="19">
@@ -3914,10 +4026,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I23" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J23" s="12" t="n"/>
     </row>
     <row r="24" ht="41.4" customHeight="1" s="19">
@@ -3956,10 +4070,12 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J24" s="12" t="n"/>
     </row>
     <row r="25" ht="41.4" customHeight="1" s="19">
@@ -3998,11 +4114,17 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>El listado suelto se reemplazó por la pestaña Hitos del centro del plan (BD/215 quitó su menú).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="41.4" customHeight="1" s="19">
       <c r="A26" s="11" t="inlineStr">
@@ -4040,11 +4162,17 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Modal sobre el centro; el plan viaja cifrado y queda fijo. Candado si la versión no está en borrador.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="27.6" customHeight="1" s="19">
       <c r="A27" s="11" t="inlineStr">
@@ -4082,10 +4210,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I27" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J27" s="12" t="n"/>
     </row>
     <row r="28" ht="27.6" customHeight="1" s="19">
@@ -4124,10 +4254,12 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J28" s="12" t="n"/>
     </row>
     <row r="29" ht="27.6" customHeight="1" s="19">
@@ -4292,11 +4424,17 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="27.6" customHeight="1" s="19">
       <c r="A33" s="11" t="inlineStr">
@@ -4334,11 +4472,17 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="27.6" customHeight="1" s="19">
       <c r="A34" s="11" t="inlineStr">
@@ -4376,11 +4520,17 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I34" s="11" t="n"/>
-      <c r="J34" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="27.6" customHeight="1" s="19">
       <c r="A35" s="11" t="inlineStr">
@@ -4418,11 +4568,17 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55.2" customHeight="1" s="19">
       <c r="A36" s="11" t="inlineStr">
@@ -4460,11 +4616,17 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="41.4" customHeight="1" s="19">
       <c r="A37" s="11" t="inlineStr">
@@ -4502,11 +4664,17 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="41.4" customHeight="1" s="19">
       <c r="A38" s="11" t="inlineStr">
@@ -4544,11 +4712,17 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>Middleware de suscripción ya existía en ApiBase (FNC_SUSCRIPCION_VIGENTE).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="27.6" customHeight="1" s="19">
       <c r="A39" s="11" t="inlineStr">
@@ -4586,11 +4760,17 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="41.4" customHeight="1" s="19">
       <c r="A40" s="11" t="inlineStr">
@@ -4628,11 +4808,17 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27.6" customHeight="1" s="19">
       <c r="A41" s="11" t="inlineStr">
@@ -4670,11 +4856,17 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="41.4" customHeight="1" s="19">
       <c r="A42" s="11" t="inlineStr">
@@ -4712,11 +4904,17 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="27.6" customHeight="1" s="19">
       <c r="A43" s="11" t="inlineStr">
@@ -5300,11 +5498,15 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
-      <c r="J56" s="12" t="n"/>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>HU-082 (actividades) es de Catalina y no está en el repo: sin actividades no hay casos que ejecutar.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="41.4" customHeight="1" s="19">
       <c r="A57" s="11" t="inlineStr">
@@ -5342,11 +5544,15 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
-      <c r="J57" s="12" t="n"/>
+      <c r="J57" s="12" t="inlineStr">
+        <is>
+          <t>Espera HU-082.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="41.4" customHeight="1" s="19">
       <c r="A58" s="11" t="inlineStr">
@@ -5384,11 +5590,15 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
-      <c r="J58" s="12" t="n"/>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Espera HU-082 y a la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="41.4" customHeight="1" s="19">
       <c r="A59" s="11" t="inlineStr">
@@ -5972,11 +6182,17 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I72" s="11" t="n"/>
-      <c r="J72" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>BD/221. Sin código: uuid + (ejecución, respuesta). Índices por cliente+estado+fecha y activo+fecha.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="41.4" customHeight="1" s="19">
       <c r="A73" s="11" t="inlineStr">
@@ -6014,10 +6230,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I73" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J73" s="12" t="n"/>
     </row>
     <row r="74" ht="41.4" customHeight="1" s="19">
@@ -6056,10 +6274,12 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J74" s="12" t="n"/>
     </row>
     <row r="75" ht="41.4" customHeight="1" s="19">
@@ -6098,10 +6318,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J75" s="12" t="n"/>
     </row>
     <row r="76" ht="41.4" customHeight="1" s="19">
@@ -6140,11 +6362,17 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>Bandeja Hallazgos de inspección: filtros, Excel, y además generar OT / descartar con motivo (BD/223) para cubrir los criterios 2 y 3.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="27.6" customHeight="1" s="19">
       <c r="A77" s="11" t="inlineStr">
@@ -6182,10 +6410,12 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I77" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J77" s="12" t="n"/>
     </row>
     <row r="78" ht="27.6" customHeight="1" s="19">
@@ -6308,10 +6538,12 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J80" s="12" t="n"/>
     </row>
     <row r="81" ht="27.6" customHeight="1" s="19">
@@ -6350,10 +6582,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J81" s="12" t="n"/>
     </row>
     <row r="82" ht="27.6" customHeight="1" s="19">
@@ -6392,11 +6626,17 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>BD/214. Valida alcance del plan (planta/tipo/modelo) contra el equipo; el combo no filtra a propósito: el SP explica.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="27.6" customHeight="1" s="19">
       <c r="A83" s="11" t="inlineStr">
@@ -6434,10 +6674,12 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J83" s="12" t="n"/>
     </row>
     <row r="84" ht="27.6" customHeight="1" s="19">
@@ -6476,11 +6718,17 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>DEL físico y no lógico: la tabla es un vínculo sin habilitado. Solo sobre borrador y sin ocurrencias.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55.2" customHeight="1" s="19">
       <c r="A85" s="11" t="inlineStr">
@@ -6518,10 +6766,12 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J85" s="12" t="n"/>
     </row>
     <row r="86" ht="41.4" customHeight="1" s="19">
@@ -6560,11 +6810,17 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>Reemplazado por la pestaña Equipos del centro del plan.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="41.4" customHeight="1" s="19">
       <c r="A87" s="11" t="inlineStr">
@@ -6602,10 +6858,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J87" s="12" t="n"/>
     </row>
     <row r="88" ht="27.6" customHeight="1" s="19">
@@ -6644,10 +6902,12 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J88" s="12" t="n"/>
     </row>
     <row r="89" ht="41.4" customHeight="1" s="19">
@@ -6686,10 +6946,12 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J89" s="12" t="n"/>
     </row>
     <row r="90" ht="41.4" customHeight="1" s="19">
@@ -7106,11 +7368,17 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="n"/>
-      <c r="J99" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>Faltaba abrir la versión siguiente: BD/219 (INS_PLAN_VERSION_NUEVA copia hitos/actividades/equipos; UPD_PLAN_VERSION_PUBLICAR). Casos en MD 10.8.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="41.4" customHeight="1" s="19">
       <c r="A100" s="11" t="inlineStr">
@@ -7148,11 +7416,17 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="n"/>
-      <c r="J100" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>MD/SIGMA_CHECKLIST_PENDIENTES.md 10.8. Sin endpoint propio: la publicación es web.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="41.4" customHeight="1" s="19">
       <c r="A101" s="11" t="inlineStr">
@@ -7610,11 +7884,15 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
-      <c r="J111" s="12" t="n"/>
+      <c r="J111" s="12" t="inlineStr">
+        <is>
+          <t>HU-091 (umbrales) la construye Catalina; sus tareas no están en el repo.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="55.2" customHeight="1" s="19">
       <c r="A112" s="11" t="inlineStr">
@@ -7652,11 +7930,15 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
-      <c r="J112" s="12" t="n"/>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>Espera HU-091 (Catalina).</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="41.4" customHeight="1" s="19">
       <c r="A113" s="11" t="inlineStr">
@@ -7694,11 +7976,15 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
-      <c r="J113" s="12" t="n"/>
+      <c r="J113" s="12" t="inlineStr">
+        <is>
+          <t>Espera HU-091 (Catalina) y a la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="41.4" customHeight="1" s="19">
       <c r="A114" s="11" t="inlineStr">
@@ -8198,11 +8484,17 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I125" s="11" t="n"/>
-      <c r="J125" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I125" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J125" s="12" t="inlineStr">
+        <is>
+          <t>probar_hu_bryan.py: POST /evidencias con uuid, lat/long y captura; reintento no duplica; queda antivirus PENDIENTE.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="41.4" customHeight="1" s="19">
       <c r="A126" s="11" t="inlineStr">
@@ -8240,11 +8532,17 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I126" s="11" t="n"/>
-      <c r="J126" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I126" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J126" s="12" t="inlineStr">
+        <is>
+          <t>MD actualizado.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="41.4" customHeight="1" s="19">
       <c r="A127" s="11" t="inlineStr">
@@ -9500,11 +9798,17 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="12" t="inlineStr">
+        <is>
+          <t>Casos ejecutados sobre SEL_PLAN_CALENDARIO (situación derivada) y generar OT desde la ocurrencia. La bandeja global es de Catalina.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="27.6" customHeight="1" s="19">
       <c r="A157" s="11" t="inlineStr">
@@ -9542,11 +9846,17 @@
       </c>
       <c r="H157" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I157" s="11" t="n"/>
-      <c r="J157" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I157" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J157" s="12" t="inlineStr">
+        <is>
+          <t>GET/POST /plan-ocurrencias documentados en XML del controlador; MD 10.5.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="27.6" customHeight="1" s="19">
       <c r="A158" s="11" t="inlineStr">
@@ -9878,11 +10188,15 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
-      <c r="J165" s="12" t="n"/>
+      <c r="J165" s="12" t="inlineStr">
+        <is>
+          <t>HU-093 (publicar plantilla) es de Emilio; espera su merge.</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="27.6" customHeight="1" s="19">
       <c r="A166" s="11" t="inlineStr">
@@ -9920,11 +10234,15 @@
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
-      <c r="J166" s="12" t="n"/>
+      <c r="J166" s="12" t="inlineStr">
+        <is>
+          <t>Espera merge de Emilio.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="27.6" customHeight="1" s="19">
       <c r="A167" s="11" t="inlineStr">
@@ -10382,11 +10700,17 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I177" s="11" t="n"/>
-      <c r="J177" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I177" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>BD/216. Sin código: única por (hito, equipo, fecha) y (programación, equipo, fecha). Dos hitos no pueden compartir programación en el mismo equipo.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="27.6" customHeight="1" s="19">
       <c r="A178" s="11" t="inlineStr">
@@ -10424,10 +10748,12 @@
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I178" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I178" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J178" s="12" t="n"/>
     </row>
     <row r="179" ht="41.4" customHeight="1" s="19">
@@ -10466,10 +10792,12 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I179" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I179" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J179" s="12" t="n"/>
     </row>
     <row r="180" ht="55.2" customHeight="1" s="19">
@@ -10508,10 +10836,12 @@
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I180" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I180" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J180" s="12" t="n"/>
     </row>
     <row r="181" ht="41.4" customHeight="1" s="19">
@@ -10550,11 +10880,17 @@
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I181" s="11" t="n"/>
-      <c r="J181" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I181" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>Pestaña Calendario del centro: año/mes/equipo/estado, solo con parada, horas por semana, Excel, generar OT y generar ocurrencias.</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="41.4" customHeight="1" s="19">
       <c r="A182" s="11" t="inlineStr">
@@ -10592,10 +10928,12 @@
       </c>
       <c r="H182" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I182" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I182" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J182" s="12" t="n"/>
     </row>
     <row r="183" ht="41.4" customHeight="1" s="19">
@@ -11768,11 +12106,17 @@
       </c>
       <c r="H210" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I210" s="11" t="n"/>
-      <c r="J210" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I210" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J210" s="12" t="inlineStr">
+        <is>
+          <t>probar_hu_bryan.py: finalizar registra duración y ejecutor; reintento con el mismo uuid -&gt; YA_ESTABA.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="27.6" customHeight="1" s="19">
       <c r="A211" s="11" t="inlineStr">
@@ -11810,11 +12154,17 @@
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I211" s="11" t="n"/>
-      <c r="J211" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>MD 10.7.</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="27.6" customHeight="1" s="19">
       <c r="A212" s="11" t="inlineStr">
@@ -12860,11 +13210,17 @@
       </c>
       <c r="H236" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I236" s="11" t="n"/>
-      <c r="J236" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I236" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J236" s="12" t="inlineStr">
+        <is>
+          <t>BD/218. Tarea solo la leía la app: se agregaron SEL/INS/UPD/DEL_TAREA con código TAR- automático.</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="27.6" customHeight="1" s="19">
       <c r="A237" s="11" t="inlineStr">
@@ -12902,11 +13258,17 @@
       </c>
       <c r="H237" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I237" s="11" t="n"/>
-      <c r="J237" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I237" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J237" s="12" t="inlineStr">
+        <is>
+          <t>Única por (tarea, programación); revive una apagada en vez de chocar con el índice.</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="55.2" customHeight="1" s="19">
       <c r="A238" s="11" t="inlineStr">
@@ -12944,10 +13306,12 @@
       </c>
       <c r="H238" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I238" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I238" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J238" s="12" t="n"/>
     </row>
     <row r="239" ht="41.4" customHeight="1" s="19">
@@ -12986,10 +13350,12 @@
       </c>
       <c r="H239" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I239" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I239" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J239" s="12" t="n"/>
     </row>
     <row r="240" ht="41.4" customHeight="1" s="19">
@@ -13028,10 +13394,12 @@
       </c>
       <c r="H240" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I240" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I240" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J240" s="12" t="n"/>
     </row>
     <row r="241" ht="27.6" customHeight="1" s="19">
@@ -13070,10 +13438,12 @@
       </c>
       <c r="H241" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I241" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I241" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J241" s="12" t="n"/>
     </row>
     <row r="242" ht="41.4" customHeight="1" s="19">
@@ -13112,11 +13482,17 @@
       </c>
       <c r="H242" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I242" s="11" t="n"/>
-      <c r="J242" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I242" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J242" s="12" t="inlineStr">
+        <is>
+          <t>Listado Tareas.aspx + centro Tarea.aspx con pestañas Ficha/Programaciones/Comentarios.</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="27.6" customHeight="1" s="19">
       <c r="A243" s="11" t="inlineStr">
@@ -13154,10 +13530,12 @@
       </c>
       <c r="H243" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I243" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I243" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J243" s="12" t="n"/>
     </row>
     <row r="244" ht="41.4" customHeight="1" s="19">
@@ -13532,11 +13910,15 @@
       </c>
       <c r="H252" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I252" s="11" t="n"/>
-      <c r="J252" s="12" t="n"/>
+      <c r="J252" s="12" t="inlineStr">
+        <is>
+          <t>HU-097 (historial de pauta) la construye Catalina; espera su desarrollo.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="55.2" customHeight="1" s="19">
       <c r="A253" s="11" t="inlineStr">
@@ -13574,11 +13956,15 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Bloqueada</t>
         </is>
       </c>
       <c r="I253" s="11" t="n"/>
-      <c r="J253" s="12" t="n"/>
+      <c r="J253" s="12" t="inlineStr">
+        <is>
+          <t>Espera HU-097 (Catalina).</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="41.4" customHeight="1" s="19">
       <c r="A254" s="11" t="inlineStr">
@@ -14120,10 +14506,12 @@
       </c>
       <c r="H266" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I266" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I266" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J266" s="12" t="n"/>
     </row>
     <row r="267" ht="41.4" customHeight="1" s="19">
@@ -14162,10 +14550,12 @@
       </c>
       <c r="H267" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I267" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I267" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J267" s="12" t="n"/>
     </row>
     <row r="268" ht="27.6" customHeight="1" s="19">
@@ -14204,10 +14594,12 @@
       </c>
       <c r="H268" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I268" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I268" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J268" s="12" t="n"/>
     </row>
     <row r="269" ht="55.2" customHeight="1" s="19">
@@ -14246,11 +14638,17 @@
       </c>
       <c r="H269" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I269" s="11" t="n"/>
-      <c r="J269" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I269" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" s="12" t="inlineStr">
+        <is>
+          <t>No aplica: Tarea_Comentario es append-only por modelo (sin habilitado ni actualización). Se responde, no se edita.</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="41.4" customHeight="1" s="19">
       <c r="A270" s="11" t="inlineStr">
@@ -14288,10 +14686,12 @@
       </c>
       <c r="H270" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I270" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I270" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J270" s="12" t="n"/>
     </row>
     <row r="271" ht="41.4" customHeight="1" s="19">
@@ -14330,11 +14730,17 @@
       </c>
       <c r="H271" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I271" s="11" t="n"/>
-      <c r="J271" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I271" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J271" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía: POST /tareas/{id}/comentarios (bloque 159, idempotente por contenido en 5 min). Verificado por HTTP (probar_hu_bryan.py).</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="27.6" customHeight="1" s="19">
       <c r="A272" s="11" t="inlineStr">
@@ -14372,11 +14778,17 @@
       </c>
       <c r="H272" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I272" s="11" t="n"/>
-      <c r="J272" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I272" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J272" s="12" t="inlineStr">
+        <is>
+          <t>Ya existía: GET /tareas/{id}/comentarios y GET /tareas/{id}. Verificado por HTTP.</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="41.4" customHeight="1" s="19">
       <c r="A273" s="11" t="inlineStr">
@@ -14414,11 +14826,17 @@
       </c>
       <c r="H273" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I273" s="11" t="n"/>
-      <c r="J273" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I273" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J273" s="12" t="inlineStr">
+        <is>
+          <t>TareaComentarioAltaDto; cuerpo vacío -&gt; 400 verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="27.6" customHeight="1" s="19">
       <c r="A274" s="11" t="inlineStr">
@@ -14456,11 +14874,17 @@
       </c>
       <c r="H274" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I274" s="11" t="n"/>
-      <c r="J274" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I274" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J274" s="12" t="inlineStr">
+        <is>
+          <t>Pestaña Comentarios del centro de la tarea: hilo como conversación con Responder/Comentar.</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="41.4" customHeight="1" s="19">
       <c r="A275" s="11" t="inlineStr">
@@ -14498,10 +14922,12 @@
       </c>
       <c r="H275" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I275" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I275" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J275" s="12" t="n"/>
     </row>
     <row r="276" ht="27.6" customHeight="1" s="19">
@@ -14540,11 +14966,17 @@
       </c>
       <c r="H276" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I276" s="11" t="n"/>
-      <c r="J276" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I276" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J276" s="12" t="inlineStr">
+        <is>
+          <t>La app ya consume el hilo en Mis tareas (sesiones anteriores).</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="27.6" customHeight="1" s="19">
       <c r="A277" s="11" t="inlineStr">
@@ -14582,10 +15014,12 @@
       </c>
       <c r="H277" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I277" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I277" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J277" s="12" t="n"/>
     </row>
     <row r="278" ht="27.6" customHeight="1" s="19">
@@ -14866,7 +15300,7 @@
       </c>
       <c r="F6" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14897,7 +15331,7 @@
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14959,7 +15393,7 @@
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15457,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15489,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15520,7 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15553,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15186,7 +15620,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15904,7 @@
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15936,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15534,7 +15968,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15565,7 +15999,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15661,7 +16095,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15692,7 +16126,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15723,7 +16157,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15786,7 +16220,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15947,7 +16381,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15979,7 +16413,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16445,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16267,7 +16701,7 @@
       </c>
       <c r="F50" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16299,7 +16733,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16331,7 +16765,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16551,7 +16985,7 @@
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16582,7 +17016,7 @@
       </c>
       <c r="F60" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16613,7 +17047,7 @@
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16740,7 +17174,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16803,7 +17237,7 @@
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16993,7 +17427,7 @@
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17152,7 +17586,7 @@
       </c>
       <c r="F78" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17183,7 +17617,7 @@
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1505,7 +1505,7 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: En revisión. Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2113,7 +2113,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P16" s="12" t="n"/>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A17" s="13" t="inlineStr">
@@ -2543,7 +2547,7 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -2551,7 +2555,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P22" s="12" t="n"/>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55.15" customHeight="1" s="19">
       <c r="A23" s="13" t="inlineStr">
@@ -2614,7 +2622,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2624,7 +2632,7 @@
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4436,7 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I32" s="11" t="n">
@@ -4436,7 +4444,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4484,7 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I33" s="11" t="n">
@@ -4484,7 +4492,7 @@
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4532,7 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I34" s="11" t="n">
@@ -4532,7 +4540,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4580,7 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I35" s="11" t="n">
@@ -4580,7 +4588,7 @@
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4628,7 @@
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I36" s="11" t="n">
@@ -4628,7 +4636,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4676,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I37" s="11" t="n">
@@ -4676,7 +4684,7 @@
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4724,7 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I38" s="11" t="n">
@@ -4724,7 +4732,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>Middleware de suscripción ya existía en ApiBase (FNC_SUSCRIPCION_VIGENTE).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Middleware de suscripción ya existía en ApiBase (FNC_SUSCRIPCION_VIGENTE).</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4772,7 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I39" s="11" t="n">
@@ -4772,7 +4780,7 @@
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4820,7 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I40" s="11" t="n">
@@ -4820,7 +4828,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4868,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I41" s="11" t="n">
@@ -4868,7 +4876,7 @@
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4916,7 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I42" s="11" t="n">
@@ -4916,7 +4924,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existía (bloques 156/157, ChecklistController, ejecucion_checklist_screen). Verificado por HTTP el 12-09: abrir idempotente, obligatorios faltantes -&gt; 400, fuera de rango, cierre con conteos.</t>
         </is>
       </c>
     </row>
@@ -4956,11 +4964,15 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I43" s="11" t="n"/>
-      <c r="J43" s="12" t="n"/>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="27.6" customHeight="1" s="19">
       <c r="A44" s="11" t="inlineStr">
@@ -4998,11 +5010,15 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I44" s="11" t="n"/>
-      <c r="J44" s="12" t="n"/>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27.6" customHeight="1" s="19">
       <c r="A45" s="11" t="inlineStr">
@@ -5040,11 +5056,15 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I45" s="11" t="n"/>
-      <c r="J45" s="12" t="n"/>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="41.45" customHeight="1" s="19">
       <c r="A46" s="11" t="inlineStr">
@@ -8066,11 +8086,15 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
-      <c r="J114" s="12" t="n"/>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="41.45" customHeight="1" s="19">
       <c r="A115" s="11" t="inlineStr">
@@ -8108,11 +8132,15 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I115" s="11" t="n"/>
-      <c r="J115" s="12" t="n"/>
+      <c r="J115" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="41.45" customHeight="1" s="19">
       <c r="A116" s="11" t="inlineStr">
@@ -8150,11 +8178,15 @@
       </c>
       <c r="H116" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I116" s="11" t="n"/>
-      <c r="J116" s="12" t="n"/>
+      <c r="J116" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="27.6" customHeight="1" s="19">
       <c r="A117" s="11" t="inlineStr">
@@ -8192,11 +8224,15 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
-      <c r="J117" s="12" t="n"/>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="27.6" customHeight="1" s="19">
       <c r="A118" s="11" t="inlineStr">
@@ -8234,11 +8270,15 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
-      <c r="J118" s="12" t="n"/>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="27.6" customHeight="1" s="19">
       <c r="A119" s="11" t="inlineStr">
@@ -8276,11 +8316,15 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I119" s="11" t="n"/>
-      <c r="J119" s="12" t="n"/>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="27.6" customHeight="1" s="19">
       <c r="A120" s="11" t="inlineStr">
@@ -8318,11 +8362,15 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
-      <c r="J120" s="12" t="n"/>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="27.6" customHeight="1" s="19">
       <c r="A121" s="11" t="inlineStr">
@@ -8360,11 +8408,15 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
-      <c r="J121" s="12" t="n"/>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="27.6" customHeight="1" s="19">
       <c r="A122" s="11" t="inlineStr">
@@ -8402,11 +8454,15 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
-      <c r="J122" s="12" t="n"/>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="55.15" customHeight="1" s="19">
       <c r="A123" s="11" t="inlineStr">
@@ -8444,11 +8500,15 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
-      <c r="J123" s="12" t="n"/>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="41.45" customHeight="1" s="19">
       <c r="A124" s="11" t="inlineStr">
@@ -8486,11 +8546,15 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I124" s="11" t="n"/>
-      <c r="J124" s="12" t="n"/>
+      <c r="J124" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="41.45" customHeight="1" s="19">
       <c r="A125" s="11" t="inlineStr">
@@ -8528,7 +8592,7 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I125" s="11" t="n">
@@ -8536,7 +8600,7 @@
       </c>
       <c r="J125" s="12" t="inlineStr">
         <is>
-          <t>probar_hu_bryan.py: POST /evidencias con uuid, lat/long y captura; reintento no duplica; queda antivirus PENDIENTE.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. probar_hu_bryan.py: POST /evidencias con uuid, lat/long y captura; reintento no duplica; queda antivirus PENDIENTE.</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8640,7 @@
       </c>
       <c r="H126" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I126" s="11" t="n">
@@ -8584,7 +8648,7 @@
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>MD actualizado.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD actualizado.</t>
         </is>
       </c>
     </row>
@@ -8624,11 +8688,15 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
-      <c r="J127" s="12" t="n"/>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="41.45" customHeight="1" s="19">
       <c r="A128" s="11" t="inlineStr">
@@ -8666,11 +8734,15 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
-      <c r="J128" s="12" t="n"/>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="41.45" customHeight="1" s="19">
       <c r="A129" s="11" t="inlineStr">
@@ -8708,11 +8780,15 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="n"/>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="41.45" customHeight="1" s="19">
       <c r="A130" s="11" t="inlineStr">
@@ -8750,11 +8826,15 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I130" s="11" t="n"/>
-      <c r="J130" s="12" t="n"/>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="27.6" customHeight="1" s="19">
       <c r="A131" s="11" t="inlineStr">
@@ -8792,11 +8872,15 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
-      <c r="J131" s="12" t="n"/>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="41.45" customHeight="1" s="19">
       <c r="A132" s="11" t="inlineStr">
@@ -8834,11 +8918,15 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
-      <c r="J132" s="12" t="n"/>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="41.45" customHeight="1" s="19">
       <c r="A133" s="11" t="inlineStr">
@@ -8876,11 +8964,15 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="n"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="41.45" customHeight="1" s="19">
       <c r="A134" s="11" t="inlineStr">
@@ -8918,11 +9010,15 @@
       </c>
       <c r="H134" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I134" s="11" t="n"/>
-      <c r="J134" s="12" t="n"/>
+      <c r="J134" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="27.6" customHeight="1" s="19">
       <c r="A135" s="11" t="inlineStr">
@@ -8960,11 +9056,15 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I135" s="11" t="n"/>
-      <c r="J135" s="12" t="n"/>
+      <c r="J135" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="27.6" customHeight="1" s="19">
       <c r="A136" s="11" t="inlineStr">
@@ -9002,11 +9102,15 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I136" s="11" t="n"/>
-      <c r="J136" s="12" t="n"/>
+      <c r="J136" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="41.45" customHeight="1" s="19">
       <c r="A137" s="11" t="inlineStr">
@@ -9044,11 +9148,15 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I137" s="11" t="n"/>
-      <c r="J137" s="12" t="n"/>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="27.6" customHeight="1" s="19">
       <c r="A138" s="11" t="inlineStr">
@@ -9086,11 +9194,15 @@
       </c>
       <c r="H138" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I138" s="11" t="n"/>
-      <c r="J138" s="12" t="n"/>
+      <c r="J138" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="55.15" customHeight="1" s="19">
       <c r="A139" s="11" t="inlineStr">
@@ -9128,11 +9240,15 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I139" s="11" t="n"/>
-      <c r="J139" s="12" t="n"/>
+      <c r="J139" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="41.45" customHeight="1" s="19">
       <c r="A140" s="11" t="inlineStr">
@@ -9170,11 +9286,15 @@
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I140" s="11" t="n"/>
-      <c r="J140" s="12" t="n"/>
+      <c r="J140" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="41.45" customHeight="1" s="19">
       <c r="A141" s="11" t="inlineStr">
@@ -11100,11 +11220,15 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
-      <c r="J185" s="12" t="n"/>
+      <c r="J185" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="27.6" customHeight="1" s="19">
       <c r="A186" s="11" t="inlineStr">
@@ -11142,11 +11266,15 @@
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
-      <c r="J186" s="12" t="n"/>
+      <c r="J186" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="27.6" customHeight="1" s="19">
       <c r="A187" s="11" t="inlineStr">
@@ -11184,11 +11312,15 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
-      <c r="J187" s="12" t="n"/>
+      <c r="J187" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="27.6" customHeight="1" s="19">
       <c r="A188" s="11" t="inlineStr">
@@ -11226,11 +11358,15 @@
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
-      <c r="J188" s="12" t="n"/>
+      <c r="J188" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="27.6" customHeight="1" s="19">
       <c r="A189" s="11" t="inlineStr">
@@ -11268,11 +11404,15 @@
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
-      <c r="J189" s="12" t="n"/>
+      <c r="J189" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="55.15" customHeight="1" s="19">
       <c r="A190" s="11" t="inlineStr">
@@ -11310,11 +11450,15 @@
       </c>
       <c r="H190" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I190" s="11" t="n"/>
-      <c r="J190" s="12" t="n"/>
+      <c r="J190" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="41.45" customHeight="1" s="19">
       <c r="A191" s="11" t="inlineStr">
@@ -11352,11 +11496,15 @@
       </c>
       <c r="H191" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I191" s="11" t="n"/>
-      <c r="J191" s="12" t="n"/>
+      <c r="J191" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="41.45" customHeight="1" s="19">
       <c r="A192" s="11" t="inlineStr">
@@ -11394,11 +11542,15 @@
       </c>
       <c r="H192" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I192" s="11" t="n"/>
-      <c r="J192" s="12" t="n"/>
+      <c r="J192" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="41.45" customHeight="1" s="19">
       <c r="A193" s="11" t="inlineStr">
@@ -11436,11 +11588,15 @@
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
-      <c r="J193" s="12" t="n"/>
+      <c r="J193" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="41.45" customHeight="1" s="19">
       <c r="A194" s="11" t="inlineStr">
@@ -11478,11 +11634,15 @@
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
-      <c r="J194" s="12" t="n"/>
+      <c r="J194" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="27.6" customHeight="1" s="19">
       <c r="A195" s="11" t="inlineStr">
@@ -11520,11 +11680,15 @@
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
-      <c r="J195" s="12" t="n"/>
+      <c r="J195" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="27.6" customHeight="1" s="19">
       <c r="A196" s="11" t="inlineStr">
@@ -11562,11 +11726,15 @@
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
-      <c r="J196" s="12" t="n"/>
+      <c r="J196" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="27.6" customHeight="1" s="19">
       <c r="A197" s="11" t="inlineStr">
@@ -11604,11 +11772,15 @@
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
-      <c r="J197" s="12" t="n"/>
+      <c r="J197" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="27.6" customHeight="1" s="19">
       <c r="A198" s="11" t="inlineStr">
@@ -11646,11 +11818,15 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
-      <c r="J198" s="12" t="n"/>
+      <c r="J198" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="27.6" customHeight="1" s="19">
       <c r="A199" s="11" t="inlineStr">
@@ -11688,11 +11864,15 @@
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
-      <c r="J199" s="12" t="n"/>
+      <c r="J199" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="41.45" customHeight="1" s="19">
       <c r="A200" s="11" t="inlineStr">
@@ -11730,11 +11910,15 @@
       </c>
       <c r="H200" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
-      <c r="J200" s="12" t="n"/>
+      <c r="J200" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="55.15" customHeight="1" s="19">
       <c r="A201" s="11" t="inlineStr">
@@ -11772,11 +11956,15 @@
       </c>
       <c r="H201" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
-      <c r="J201" s="12" t="n"/>
+      <c r="J201" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="41.45" customHeight="1" s="19">
       <c r="A202" s="11" t="inlineStr">
@@ -11814,11 +12002,15 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
-      <c r="J202" s="12" t="n"/>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="41.45" customHeight="1" s="19">
       <c r="A203" s="11" t="inlineStr">
@@ -11856,11 +12048,15 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
-      <c r="J203" s="12" t="n"/>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="41.45" customHeight="1" s="19">
       <c r="A204" s="11" t="inlineStr">
@@ -11898,11 +12094,15 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
-      <c r="J204" s="12" t="n"/>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="41.45" customHeight="1" s="19">
       <c r="A205" s="11" t="inlineStr">
@@ -11940,11 +12140,15 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
-      <c r="J205" s="12" t="n"/>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="27.6" customHeight="1" s="19">
       <c r="A206" s="11" t="inlineStr">
@@ -11982,11 +12186,15 @@
       </c>
       <c r="H206" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
-      <c r="J206" s="12" t="n"/>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="27.6" customHeight="1" s="19">
       <c r="A207" s="11" t="inlineStr">
@@ -12024,11 +12232,15 @@
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
-      <c r="J207" s="12" t="n"/>
+      <c r="J207" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="27.6" customHeight="1" s="19">
       <c r="A208" s="11" t="inlineStr">
@@ -12066,11 +12278,15 @@
       </c>
       <c r="H208" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I208" s="11" t="n"/>
-      <c r="J208" s="12" t="n"/>
+      <c r="J208" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="41.45" customHeight="1" s="19">
       <c r="A209" s="11" t="inlineStr">
@@ -12108,11 +12324,15 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I209" s="11" t="n"/>
-      <c r="J209" s="12" t="n"/>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="27.6" customHeight="1" s="19">
       <c r="A210" s="11" t="inlineStr">
@@ -12150,7 +12370,7 @@
       </c>
       <c r="H210" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I210" s="11" t="n">
@@ -12158,7 +12378,7 @@
       </c>
       <c r="J210" s="12" t="inlineStr">
         <is>
-          <t>probar_hu_bryan.py: finalizar registra duración y ejecutor; reintento con el mismo uuid -&gt; YA_ESTABA.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. probar_hu_bryan.py: finalizar registra duración y ejecutor; reintento con el mismo uuid -&gt; YA_ESTABA.</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12418,7 @@
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I211" s="11" t="n">
@@ -12206,7 +12426,7 @@
       </c>
       <c r="J211" s="12" t="inlineStr">
         <is>
-          <t>MD 10.7.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. MD 10.7.</t>
         </is>
       </c>
     </row>
@@ -15010,7 +15230,7 @@
       </c>
       <c r="H276" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I276" s="11" t="n">
@@ -15018,7 +15238,7 @@
       </c>
       <c r="J276" s="12" t="inlineStr">
         <is>
-          <t>La app ya consume el hilo en Mis tareas (sesiones anteriores).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. La app ya consume el hilo en Mis tareas (sesiones anteriores).</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -254,6 +254,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1166,6 +1169,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1603,7 +1608,7 @@
       </c>
       <c r="P10" s="17" t="inlineStr">
         <is>
-          <t>Construida por Emilio Fuentes (11-09-2026) siguiendo PATRONES/ASP: BD SEL/INS/UPD/DEL_CHECKLIST_PLANTILLA (patron dinamico, FNC_PAIS_HORA, INS_EXCEPCION, codigo unico por cliente, baja logica) + estructura Version/Seccion/Item/Validacion (BD/192) + lookups (BD/189,191,194). Web: ChecklistPlantillas/ChecklistPlantilla/ChecklistPlantillaVista con Model+Controllers; editor inline de secciones y campos; previsualizacion de solo lectura al clic. Datos reales: SOP-09-R24 con 25 secciones y 208 campos (BD/193). Seguridad por cliente + Token + Menu_Funcion. Compila exitcode=0 y SP probados en transaccion revertida. PENDIENTE (otra persona): pruebas por criterio, documentacion y consumo movil.</t>
+          <t>Construida por Emilio Fuentes (11-09-2026) siguiendo PATRONES/ASP: BD SEL/INS/UPD/DEL_CHECKLIST_PLANTILLA (patron dinamico, FNC_PAIS_HORA, INS_EXCEPCION, codigo unico por cliente, baja logica) + estructura Version/Seccion/Item/Validacion (BD/192) + lookups (BD/189,191,194). Web: ChecklistPlantillas/ChecklistPlantilla/ChecklistPlantillaVista con Model+Controllers; editor inline de secciones y campos; previsualizacion de solo lectura al clic. Datos reales: SOP-09-R24 con 25 secciones y 208 campos (BD/193). Seguridad por cliente + Token + Menu_Funcion. Compila exitcode=0 y SP probados en transaccion revertida. PENDIENTE (otra persona): pruebas por criterio, documentacion y consumo movil. || AJUSTE 21-09-2026 (Emilio Fuentes): se unifico el termino en la interfaz a "Pauta de inspeccion" y se quito "checklist" del texto visible (titulo de la ficha, seccion "Campos de la pauta", ayudas y mensajes de exito). Los nombres tecnicos internos (tablas Checklist_*, SP, clases, archivos) NO cambian; es solo lenguaje de cara al usuario para no mezclar "pauta" y "checklist".</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1815,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1818,7 +1823,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P13" s="14" t="n"/>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>BD (SPs+índices+datos), Web PlanVersion.aspx y Seguridad terminadas (Emilio). Pendiente: pruebas (T-4119) y documentación (T-4120) de Bryan.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -2027,7 +2036,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2035,7 +2044,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P16" s="12" t="n"/>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Backend terminado (Emilio): BD (SEL/INS/datos+índices), API GET/POST /dictado-voz/sync, middleware de suscripción 402 y seguridad. Pendiente: móvil Flutter (T-4160/61/62) y pruebas/doc/validación de Catalina (T-4164/65/66).</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="96.59999999999999" customHeight="1" s="19">
       <c r="A17" s="13" t="inlineStr">
@@ -2098,7 +2111,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -2106,7 +2119,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P17" s="14" t="n"/>
+      <c r="P17" s="14" t="inlineStr">
+        <is>
+          <t>BD (SP reprogramar+SEL+datos), Web PlanOcurrenciaReprogramar.aspx y Seguridad terminadas (Emilio). Pendiente pruebas/documentación.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55.2" customHeight="1" s="19">
       <c r="A18" s="11" t="inlineStr">
@@ -2240,7 +2257,7 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -2248,7 +2265,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P19" s="14" t="n"/>
+      <c r="P19" s="26" t="inlineStr">
+        <is>
+          <t>Construida por Emilio Fuentes (21-09-2026): BD PUBLICAR_CHECKLIST_VERSION (proceso en transaccion, retira publicada anterior, rechaza sin items, sella quien/cuando) + SEL_CHECKLIST_VERSION (BD/195,196). Web ChecklistVersion.aspx abierta desde el listado de Pautas. Seguridad por cliente + Token. Compila exitcode=0; proceso verificado en transaccion revertida. PENDIENTE (Bryan): pruebas y documentacion.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="69" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -2311,7 +2332,7 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -2319,7 +2340,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P20" s="12" t="n"/>
+      <c r="P20" s="17" t="inlineStr">
+        <is>
+          <t>Construida por Emilio Fuentes (22-09-2026): BD SEL/INS/UPD_CHECKLIST_PROGRAMACION (resuelve version publicada, exige activo O area, FNC_PAIS_HORA, patron dinamico) + datos de prueba (BD/197, 198). Web ChecklistProgramacions/ChecklistProgramacion con Model+Controller; combos por SEL_. Seguridad por cliente + Token. Compila exitcode=0; CA3 verificado en transaccion revertida. NOTA: para programar una pauta debe estar PUBLICADA (HU-093). PENDIENTE (Catalina): pruebas y documentacion.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55.2" customHeight="1" s="19">
       <c r="A21" s="13" t="inlineStr">
@@ -2524,7 +2549,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2532,7 +2557,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P23" s="14" t="n"/>
+      <c r="P23" s="14" t="inlineStr">
+        <is>
+          <t>BD (SEL+datos+modelo) y Seguridad terminadas (Emilio). API (GET/POST sync + middleware) en revisión, para otro momento. Móvil y pruebas/doc según reparto.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="69" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -2879,7 +2908,7 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -2887,7 +2916,11 @@
           <t>Emilio Fuentes</t>
         </is>
       </c>
-      <c r="P28" s="12" t="n"/>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>BD (modelo+SEL/INS/UPD/DEL+datos), Web (listado+ficha+menú) y Seguridad terminadas (Emilio). Pendiente pruebas/documentación.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55.2" customHeight="1" s="19">
       <c r="A29" s="13" t="inlineStr">
@@ -3070,8 +3103,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -6812,11 +6843,15 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I92" s="11" t="n"/>
-      <c r="J92" s="12" t="n"/>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>Índices únicos verificados: UX_PMA_CLIENTE_CODIGO (código por cliente) y UX_PMV_PLAN_NUMERO (número por plan). Modelo Plan_Mantenimiento_Version OK.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="27.6" customHeight="1" s="19">
       <c r="A93" s="11" t="inlineStr">
@@ -6854,11 +6889,15 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I93" s="11" t="n"/>
-      <c r="J93" s="12" t="n"/>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>Endurecido en BD/199: SET XACT_ABORT ON en UPD_PLAN_MANTENIMIENTO_VERSION_PUBLICAR y UPD_PLAN_VERSION_PUBLICAR. Publica dentro de transacción con TRY/CATCH; cualquier error revierte todo.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="27.6" customHeight="1" s="19">
       <c r="A94" s="11" t="inlineStr">
@@ -6896,11 +6935,15 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I94" s="11" t="n"/>
-      <c r="J94" s="12" t="n"/>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>Reglas en el SP (existe, es borrador, exige hitos y equipos, decide la carrera en el UPDATE del borrador). Verificado: rechaza sin hitos (msg 3) y de otro cliente (msg 1).</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="27.6" customHeight="1" s="19">
       <c r="A95" s="11" t="inlineStr">
@@ -6938,11 +6981,15 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I95" s="11" t="n"/>
-      <c r="J95" s="12" t="n"/>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>SEL_PLAN_VERSION devuelve el historial + código/nombre del plan, conteos (hitos/activos/ocurrencias) y usuarios. Lo consume PlanVersionController.GetVersiones.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55.2" customHeight="1" s="19">
       <c r="A96" s="11" t="inlineStr">
@@ -6980,11 +7027,15 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
-      <c r="J96" s="12" t="n"/>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>Datos de prueba presentes: planes PMA-* con versiones en BORRADOR/PUBLICADO/RETIRADO. Publicación probada en transacción revertida (pmv 2 → PUBLICADO, sella usuario y observación).</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="41.4" customHeight="1" s="19">
       <c r="A97" s="11" t="inlineStr">
@@ -7022,11 +7073,15 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
-      <c r="J97" s="12" t="n"/>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>Web PlanVersion.aspx creada en View/Mantenimiento/Planes/: historial de versiones + publicar el borrador, mostrando quién publicó y cuándo. Modelo PlanVersion + PlanVersionController. Compila exitcode 0.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="41.4" customHeight="1" s="19">
       <c r="A98" s="11" t="inlineStr">
@@ -7064,11 +7119,15 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
-      <c r="J98" s="12" t="n"/>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>Seguridad server-side: Token.Puede('CREAR EDITAR PLANES MANTENIMIENTO') revalidado en btnPublicar_Click (no se esconde el botón). Página registrada en Menus con permiso VER PLANES MANTENIMIENTO (BD/200). Filtro por cliente en el SP.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="41.4" customHeight="1" s="19">
       <c r="A99" s="11" t="inlineStr">
@@ -8282,11 +8341,15 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
-      <c r="J127" s="12" t="n"/>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Modelo verificado: Dictado_Voz existe. Su clave natural es el UUID del teléfono (no un código por cliente); el índice único UX_DVO_UUID hace idempotente la recepción. IX_DVO_CLIENTE_FECHA presente.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="41.4" customHeight="1" s="19">
       <c r="A128" s="11" t="inlineStr">
@@ -8324,11 +8387,15 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
-      <c r="J128" s="12" t="n"/>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>BD/201: API_SEL_DICTADO_VOZ (descarga acotada al usuario y su cliente, incremental por @DESDE). Probado: devuelve el dictado del usuario demo.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="41.4" customHeight="1" s="19">
       <c r="A129" s="11" t="inlineStr">
@@ -8366,11 +8433,15 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="n"/>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>API_INS_DICTADO_VOZ verificado: idempotente por UUID (si el UUID ya existe devuelve el mismo id, no inserta un segundo). El audio no se guarda; nace en PROCESADO.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="41.4" customHeight="1" s="19">
       <c r="A130" s="11" t="inlineStr">
@@ -8408,11 +8479,15 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I130" s="11" t="n"/>
-      <c r="J130" s="12" t="n"/>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>BD/201: datos de prueba (2 dictados del usuario del cliente 1 con UUID fijos, reaplicables). Cliente 1 con dictados para ejercitar los CA.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="27.6" customHeight="1" s="19">
       <c r="A131" s="11" t="inlineStr">
@@ -8450,11 +8525,15 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
-      <c r="J131" s="12" t="n"/>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>API GET /dictado-voz/sync — descarga para el dispositivo, identidad del token (usuario+cliente), incremental por ?desde. Compila (MSBuild exit 0).</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="41.4" customHeight="1" s="19">
       <c r="A132" s="11" t="inlineStr">
@@ -8492,11 +8571,15 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
-      <c r="J132" s="12" t="n"/>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>API POST /dictado-voz/sync — subida por lotes, idempotente por uuid (reenvío devuelve el mismo id). Identidad del token, nunca del cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="41.4" customHeight="1" s="19">
       <c r="A133" s="11" t="inlineStr">
@@ -8534,11 +8617,15 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="n"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>Middleware SuscripcionVigenteHandler (registrado en WebApiConfig): valida la KEY del cliente (X-Cliente-Key) contra FNC_SUSCRIPCION_VIGENTE (vía API_SEL_SUSCRIPCION_VIGENTE) y responde 402 si no puede operar. Sin la KEY no corta (no rompe a nadie). Probado: hash real → PUEDE_OPERAR=1; hash inexistente → vacío → 402.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="41.4" customHeight="1" s="19">
       <c r="A134" s="11" t="inlineStr">
@@ -8702,11 +8789,15 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I137" s="11" t="n"/>
-      <c r="J137" s="12" t="n"/>
+      <c r="J137" s="12" t="inlineStr">
+        <is>
+          <t>Seguridad server-side: identidad del token (ExigirUsuario) + acotado por cliente (ExigirCliente); el dictado no es un recurso con permiso propio (es ambiente a cualquier campo que el usuario ya edita), así que no se esconde nada por CSS y la suscripción la corta el 402 del middleware.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="27.6" customHeight="1" s="19">
       <c r="A138" s="11" t="inlineStr">
@@ -8870,11 +8961,15 @@
       </c>
       <c r="H141" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I141" s="11" t="n"/>
-      <c r="J141" s="12" t="n"/>
+      <c r="J141" s="12" t="inlineStr">
+        <is>
+          <t>Modelo verificado: Plan_Mantenimiento_Ocurrencia con índices únicos UX_PMO_UUID, UX_PMO_HITO_ACTIVO_FECHA y UX_PMO_PROGRAMACION_ACTIVO_FECHA (impiden dos ocurrencias del mismo hito/equipo en la misma fecha). No hay 'código'; la clave es hito+activo+fecha.</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="27.6" customHeight="1" s="19">
       <c r="A142" s="11" t="inlineStr">
@@ -8912,11 +9007,15 @@
       </c>
       <c r="H142" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I142" s="11" t="n"/>
-      <c r="J142" s="12" t="n"/>
+      <c r="J142" s="12" t="inlineStr">
+        <is>
+          <t>BD/202: PLAN_OCURRENCIA_REPROGRAMAR con SET XACT_ABORT ON; todo el proceso (retirar la vieja a REPROGRAMADA + crear la nueva PENDIENTE ligada por origen) en una transacción con TRY/CATCH.</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="27.6" customHeight="1" s="19">
       <c r="A143" s="11" t="inlineStr">
@@ -8954,11 +9053,15 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I143" s="11" t="n"/>
-      <c r="J143" s="12" t="n"/>
+      <c r="J143" s="12" t="inlineStr">
+        <is>
+          <t>Reglas en el SP: solo reprograma PENDIENTE/DISPONIBLE, motivo obligatorio, fecha distinta, sin colisión de fecha, y decide la carrera en el UPDATE. Verificado: rechazos 1 (no existe/cliente ajeno), 2 (estado), 3 (motivo).</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="27.6" customHeight="1" s="19">
       <c r="A144" s="11" t="inlineStr">
@@ -8996,11 +9099,15 @@
       </c>
       <c r="H144" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I144" s="11" t="n"/>
-      <c r="J144" s="12" t="n"/>
+      <c r="J144" s="12" t="inlineStr">
+        <is>
+          <t>BD/202: SEL_PLAN_OCURRENCIA_REPROGRAMAR devuelve la ficha (activo/hito/plan, estado, fecha programada/original) y el resultado (a qué fecha se movió, la nueva ocurrencia, quién y cuándo).</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="41.4" customHeight="1" s="19">
       <c r="A145" s="11" t="inlineStr">
@@ -9038,11 +9145,15 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I145" s="11" t="n"/>
-      <c r="J145" s="12" t="n"/>
+      <c r="J145" s="12" t="inlineStr">
+        <is>
+          <t>BD/202: datos de prueba (una ocurrencia reprogramada, siembra idempotente). Además ya existían decenas de ocurrencias PENDIENTE del plan de hornos para ejercitar los CA.</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="27.6" customHeight="1" s="19">
       <c r="A146" s="11" t="inlineStr">
@@ -9080,11 +9191,15 @@
       </c>
       <c r="H146" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I146" s="11" t="n"/>
-      <c r="J146" s="12" t="n"/>
+      <c r="J146" s="12" t="inlineStr">
+        <is>
+          <t>Web PlanOcurrenciaReprogramar.aspx (View/Mantenimiento/Planes/): muestra la ocurrencia, permite mover a nueva fecha con motivo obligatorio, y muestra el resultado (movida a X por quién). Modelo PlanOcurrencia + PlanOcurrenciaController. Compila exitcode 0.</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="27.6" customHeight="1" s="19">
       <c r="A147" s="11" t="inlineStr">
@@ -9122,11 +9237,15 @@
       </c>
       <c r="H147" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I147" s="11" t="n"/>
-      <c r="J147" s="12" t="n"/>
+      <c r="J147" s="12" t="inlineStr">
+        <is>
+          <t>Seguridad server-side: Token.Puede('CREAR EDITAR PLANES MANTENIMIENTO') revalidado en btnReprogramar_Click (no se esconde el botón). Página registrada en Menus con permiso VER PLANES MANTENIMIENTO (BD/203). Filtro por cliente en el SP.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="27.6" customHeight="1" s="19">
       <c r="A148" s="11" t="inlineStr">
@@ -9584,11 +9703,15 @@
       </c>
       <c r="H158" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I158" s="11" t="n"/>
-      <c r="J158" s="12" t="n"/>
+      <c r="J158" s="17" t="inlineStr">
+        <is>
+          <t>Revisado Checklist_Plantilla_Version; confirmado el unico UX_CPV_PLANTILLA_NUMERO. BD/195.</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="41.4" customHeight="1" s="19">
       <c r="A159" s="11" t="inlineStr">
@@ -9626,11 +9749,15 @@
       </c>
       <c r="H159" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I159" s="11" t="n"/>
-      <c r="J159" s="12" t="n"/>
+      <c r="J159" s="17" t="inlineStr">
+        <is>
+          <t>PUBLICAR_CHECKLIST_VERSION: proceso en transaccion con SET XACT_ABORT ON; FNC_PAIS_HORA + INS_EXCEPCION. BD/195.</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="27.6" customHeight="1" s="19">
       <c r="A160" s="11" t="inlineStr">
@@ -9668,11 +9795,15 @@
       </c>
       <c r="H160" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I160" s="11" t="n"/>
-      <c r="J160" s="12" t="n"/>
+      <c r="J160" s="17" t="inlineStr">
+        <is>
+          <t>Reglas en el SP: retira la publicada anterior (CA1), registra quien/cuando, rechaza publicar sin items (CA2). BD/195.</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="27.6" customHeight="1" s="19">
       <c r="A161" s="11" t="inlineStr">
@@ -9710,11 +9841,15 @@
       </c>
       <c r="H161" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I161" s="11" t="n"/>
-      <c r="J161" s="12" t="n"/>
+      <c r="J161" s="17" t="inlineStr">
+        <is>
+          <t>SEL_CHECKLIST_VERSION: historial de versiones por pauta, filtrado por cliente. BD/195.</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="27.6" customHeight="1" s="19">
       <c r="A162" s="11" t="inlineStr">
@@ -9752,11 +9887,15 @@
       </c>
       <c r="H162" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I162" s="11" t="n"/>
-      <c r="J162" s="12" t="n"/>
+      <c r="J162" s="17" t="inlineStr">
+        <is>
+          <t>Datos de prueba: borrador de SOP-09-R24 (208 items) publicable; rechazos verificados en transaccion revertida. BD/195.</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="41.4" customHeight="1" s="19">
       <c r="A163" s="11" t="inlineStr">
@@ -9794,11 +9933,15 @@
       </c>
       <c r="H163" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I163" s="11" t="n"/>
-      <c r="J163" s="12" t="n"/>
+      <c r="J163" s="17" t="inlineStr">
+        <is>
+          <t>ChecklistVersion.aspx: historial + publicar borrador, abierta desde el listado de Pautas. Model+Controller ChecklistVersion.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="55.2" customHeight="1" s="19">
       <c r="A164" s="11" t="inlineStr">
@@ -9836,11 +9979,15 @@
       </c>
       <c r="H164" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I164" s="11" t="n"/>
-      <c r="J164" s="12" t="n"/>
+      <c r="J164" s="17" t="inlineStr">
+        <is>
+          <t>Seguridad: VER PAUTAS para abrir (Menus BD/196) + Token.Puede("CREAR EDITAR PAUTAS") para publicar; SP filtra por cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="27.6" customHeight="1" s="19">
       <c r="A165" s="11" t="inlineStr">
@@ -9962,11 +10109,15 @@
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I167" s="11" t="n"/>
-      <c r="J167" s="12" t="n"/>
+      <c r="J167" s="17" t="inlineStr">
+        <is>
+          <t>Revisado Checklist_Programacion (FK a version, programacion, activo, area, grupo, responsable). PK cpr_id; no hay unico natural (una version se programa en varios objetivos). BD/197.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="55.2" customHeight="1" s="19">
       <c r="A168" s="11" t="inlineStr">
@@ -10004,11 +10155,15 @@
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I168" s="11" t="n"/>
-      <c r="J168" s="12" t="n"/>
+      <c r="J168" s="17" t="inlineStr">
+        <is>
+          <t>INS_CHECKLIST_PROGRAMACION: alta en transaccion; resuelve la version PUBLICADA de la pauta; exige activo O area (CA3); valida objetivo del cliente; FNC_PAIS_HORA + INS_EXCEPCION. BD/197.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="41.4" customHeight="1" s="19">
       <c r="A169" s="11" t="inlineStr">
@@ -10046,11 +10201,15 @@
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I169" s="11" t="n"/>
-      <c r="J169" s="12" t="n"/>
+      <c r="J169" s="17" t="inlineStr">
+        <is>
+          <t>SEL_CHECKLIST_PROGRAMACION: patron dinamico @SELECT/@FROM/@WHERE con nombres de pauta/recurrencia/objetivo/responsable; un solo SP grilla+ficha. BD/197.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="41.4" customHeight="1" s="19">
       <c r="A170" s="11" t="inlineStr">
@@ -10088,11 +10247,15 @@
       </c>
       <c r="H170" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I170" s="11" t="n"/>
-      <c r="J170" s="12" t="n"/>
+      <c r="J170" s="17" t="inlineStr">
+        <is>
+          <t>UPD_CHECKLIST_PROGRAMACION: @ID/@USUARIO obligatorios, ISNULL en lo opcional, conserva la regla activo/area; puede cambiar pauta (re-resuelve version publicada). BD/197.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="27.6" customHeight="1" s="19">
       <c r="A171" s="11" t="inlineStr">
@@ -10130,11 +10293,15 @@
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I171" s="11" t="n"/>
-      <c r="J171" s="12" t="n"/>
+      <c r="J171" s="17" t="inlineStr">
+        <is>
+          <t>Datos de prueba: se publico SOP-09-R24 y se creo la programacion "Ronda diaria - Revolvedora 1"; CA3 (sin objetivo) verificado en transaccion revertida. BD/197.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="41.4" customHeight="1" s="19">
       <c r="A172" s="11" t="inlineStr">
@@ -10172,11 +10339,15 @@
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I172" s="11" t="n"/>
-      <c r="J172" s="12" t="n"/>
+      <c r="J172" s="17" t="inlineStr">
+        <is>
+          <t>ChecklistProgramacion.aspx (RadWindow, sigma-modal-* seccionada: Identificacion, Objetivo, Asignacion); combos Pauta(publicadas)/Recurrencia/Activo/Area/Grupo/Responsable por SEL_; validaciones + wuc:Auditoria.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="55.2" customHeight="1" s="19">
       <c r="A173" s="11" t="inlineStr">
@@ -10214,11 +10385,15 @@
       </c>
       <c r="H173" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I173" s="11" t="n"/>
-      <c r="J173" s="12" t="n"/>
+      <c r="J173" s="17" t="inlineStr">
+        <is>
+          <t>ChecklistProgramacions.aspx: grilla + wucFiltro (habilitado) + Nuevo/Dar de baja; columna Objetivo (activo o area) y pauta con su version. Model+Controller ChecklistProgramacion.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="27.6" customHeight="1" s="19">
       <c r="A174" s="11" t="inlineStr">
@@ -10256,11 +10431,15 @@
       </c>
       <c r="H174" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I174" s="11" t="n"/>
-      <c r="J174" s="12" t="n"/>
+      <c r="J174" s="17" t="inlineStr">
+        <is>
+          <t>Seguridad: VER PAUTAS para abrir (Menus BD/198) + Token.Puede("CREAR EDITAR PAUTAS") en la ficha; SEL/INS/UPD filtran por cliente.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="27.6" customHeight="1" s="19">
       <c r="A175" s="11" t="inlineStr">
@@ -11306,11 +11485,15 @@
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I199" s="11" t="n"/>
-      <c r="J199" s="12" t="n"/>
+      <c r="J199" s="12" t="inlineStr">
+        <is>
+          <t>Modelo verificado: Tarea_Ejecucion con UX_TEJ_UUID (idempotencia por uuid). Sin columna de cliente: el cliente sale por tej_tarea_ocurrencia -&gt; Tarea_Ocurrencia. No hay 'código por cliente'.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="41.4" customHeight="1" s="19">
       <c r="A200" s="11" t="inlineStr">
@@ -11348,11 +11531,15 @@
       </c>
       <c r="H200" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
-      <c r="J200" s="12" t="n"/>
+      <c r="J200" s="12" t="inlineStr">
+        <is>
+          <t>BD/204: SEL_TAREA_EJECUCION (descarga acotada al usuario, su cliente y las plantas donde está asignado, incremental por @DESDE). Probado: usuario 7 baja su ejecución; usuario sin planta no baja nada.</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="55.2" customHeight="1" s="19">
       <c r="A201" s="11" t="inlineStr">
@@ -11390,11 +11577,15 @@
       </c>
       <c r="H201" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I201" s="11" t="n"/>
-      <c r="J201" s="12" t="n"/>
+      <c r="J201" s="12" t="inlineStr">
+        <is>
+          <t>Verificado: API_UPS_TAREA_EJECUCION es idempotente por uuid (busca por uuid antes de mirar el estado; el reenvío de un cierre ya grabado no duplica ni da error falso).</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="41.4" customHeight="1" s="19">
       <c r="A202" s="11" t="inlineStr">
@@ -11432,11 +11623,15 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
-      <c r="J202" s="12" t="n"/>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>BD/204: datos de prueba (una ejecución cerrada del usuario 7 sobre la ocurrencia 1, uuid fijo, idempotente). Ya existían 8 ejecuciones más.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="41.4" customHeight="1" s="19">
       <c r="A203" s="11" t="inlineStr">
@@ -11474,11 +11669,15 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
-      <c r="J203" s="12" t="n"/>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente (por indicación, para otro momento). El middleware de suscripción global (SuscripcionVigenteHandler, HU-160) ya aplica a estos endpoints cuando se construyan.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="41.4" customHeight="1" s="19">
       <c r="A204" s="11" t="inlineStr">
@@ -11516,11 +11715,15 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
-      <c r="J204" s="12" t="n"/>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente (por indicación, para otro momento). El middleware de suscripción global (SuscripcionVigenteHandler, HU-160) ya aplica a estos endpoints cuando se construyan.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="41.4" customHeight="1" s="19">
       <c r="A205" s="11" t="inlineStr">
@@ -11558,11 +11761,15 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
-      <c r="J205" s="12" t="n"/>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente (por indicación, para otro momento). El middleware de suscripción global (SuscripcionVigenteHandler, HU-160) ya aplica a estos endpoints cuando se construyan.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="27.6" customHeight="1" s="19">
       <c r="A206" s="11" t="inlineStr">
@@ -11726,11 +11933,15 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I209" s="11" t="n"/>
-      <c r="J209" s="12" t="n"/>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Seguridad a nivel de datos: SEL/UPS acotan por cliente + usuario + planta (Cliente_Instalacion_Usuario); un usuario no ve ni escribe ejecuciones de una planta a la que no pertenece. Verificado: usuario sin planta obtiene 0 filas.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="27.6" customHeight="1" s="19">
       <c r="A210" s="11" t="inlineStr">
@@ -13616,11 +13827,15 @@
       </c>
       <c r="H254" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I254" s="11" t="n"/>
-      <c r="J254" s="12" t="n"/>
+      <c r="J254" s="12" t="inlineStr">
+        <is>
+          <t>Modelo alineado (BD/205): se quitó UX_TCA_GLOBAL_CODIGO (código único global, que contradecía el criterio) y quedó UX_TCA_CLIENTE_CODIGO (único por cliente). Tabla estaba vacía.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="41.4" customHeight="1" s="19">
       <c r="A255" s="11" t="inlineStr">
@@ -13658,11 +13873,15 @@
       </c>
       <c r="H255" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I255" s="11" t="n"/>
-      <c r="J255" s="12" t="n"/>
+      <c r="J255" s="12" t="inlineStr">
+        <is>
+          <t>BD/205: SEL_TAREA_CATEGORIA reescrito (el anterior estaba roto: columnas TCA_USUARIO_ACT/TCA_FECHA_ACT inexistentes, sin filtro por cliente, sin escapar). Un solo SP para grilla y ficha; filtros @ID/@CLIENTE/@FILTRO/@HABILITADO; @FILTRO escapado; ORDER BY estable (orden, código).</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="41.4" customHeight="1" s="19">
       <c r="A256" s="11" t="inlineStr">
@@ -13700,11 +13919,15 @@
       </c>
       <c r="H256" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I256" s="11" t="n"/>
-      <c r="J256" s="12" t="n"/>
+      <c r="J256" s="12" t="inlineStr">
+        <is>
+          <t>BD/205: INS_TAREA_CATEGORIA en transacción, valida código único por cliente, sella con FNC_PAIS_HORA. Verificado: rechaza código duplicado (msg 2) y normaliza a mayúsculas.</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="41.4" customHeight="1" s="19">
       <c r="A257" s="11" t="inlineStr">
@@ -13742,11 +13965,15 @@
       </c>
       <c r="H257" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I257" s="11" t="n"/>
-      <c r="J257" s="12" t="n"/>
+      <c r="J257" s="12" t="inlineStr">
+        <is>
+          <t>BD/205: UPD_TAREA_CATEGORIA con ISNULL(@X, columna) (lo que la ficha no manda se conserva) y código único por cliente excluyendo el propio. Verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="41.4" customHeight="1" s="19">
       <c r="A258" s="11" t="inlineStr">
@@ -13784,11 +14011,15 @@
       </c>
       <c r="H258" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I258" s="11" t="n"/>
-      <c r="J258" s="12" t="n"/>
+      <c r="J258" s="12" t="inlineStr">
+        <is>
+          <t>BD/205: DEL_TAREA_CATEGORIA baja lógica (tca_habilitado=0); rechaza si la categoría tiene tareas asociadas (tar_tarea_categoria) en vez de dejarlas huérfanas. Verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="41.4" customHeight="1" s="19">
       <c r="A259" s="11" t="inlineStr">
@@ -13826,11 +14057,15 @@
       </c>
       <c r="H259" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I259" s="11" t="n"/>
-      <c r="J259" s="12" t="n"/>
+      <c r="J259" s="12" t="inlineStr">
+        <is>
+          <t>BD/205: datos de prueba (PREVENTIVO/CORRECTIVO/INSPECCION del cliente 1, con color y orden; idempotentes por código).</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="41.4" customHeight="1" s="19">
       <c r="A260" s="11" t="inlineStr">
@@ -13868,11 +14103,15 @@
       </c>
       <c r="H260" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I260" s="11" t="n"/>
-      <c r="J260" s="12" t="n"/>
+      <c r="J260" s="12" t="inlineStr">
+        <is>
+          <t>Web TareaCategorias.aspx: grilla con búsqueda, filtro de habilitados y botón Nuevo; muestra el color como muestra. Compila exitcode 0.</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="27.6" customHeight="1" s="19">
       <c r="A261" s="11" t="inlineStr">
@@ -13910,11 +14149,15 @@
       </c>
       <c r="H261" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I261" s="11" t="n"/>
-      <c r="J261" s="12" t="n"/>
+      <c r="J261" s="12" t="inlineStr">
+        <is>
+          <t>Web TareaCategoria.aspx en RadWindow (SigmaModal) con clases sigma-modal-*: código/nombre/color/orden/habilitado, validadores y Guardar/Cerrar.</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="41.4" customHeight="1" s="19">
       <c r="A262" s="11" t="inlineStr">
@@ -13952,11 +14195,15 @@
       </c>
       <c r="H262" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I262" s="11" t="n"/>
-      <c r="J262" s="12" t="n"/>
+      <c r="J262" s="12" t="inlineStr">
+        <is>
+          <t>BD/206: registra listado (visible) y ficha (oculta) en Menus con permiso VER TAREAS; sin fila en Menus la pantalla no se abre.</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="55.2" customHeight="1" s="19">
       <c r="A263" s="11" t="inlineStr">
@@ -13994,11 +14241,15 @@
       </c>
       <c r="H263" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I263" s="11" t="n"/>
-      <c r="J263" s="12" t="n"/>
+      <c r="J263" s="12" t="inlineStr">
+        <is>
+          <t>Seguridad server-side: Token.Puede('CREAR EDITAR TAREAS') revalidado en btnGuardar_Click (no se esconde el botón); función Crear y editar en Menu_Funcion; SEL/listado filtran por cliente en sesión.</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="41.4" customHeight="1" s="19">
       <c r="A264" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -12356,7 +12356,7 @@
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I224" s="11" t="n"/>
@@ -12398,7 +12398,7 @@
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I225" s="11" t="n"/>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I226" s="11" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I227" s="11" t="n"/>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I228" s="11" t="n"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="H230" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I230" s="11" t="n"/>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I231" s="11" t="n"/>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H232" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I232" s="11" t="n"/>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I233" s="11" t="n"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -3744,7 +3744,11 @@
         </is>
       </c>
       <c r="I16" s="11" t="n"/>
-      <c r="J16" s="12" t="n"/>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="41.45" customHeight="1" s="19">
       <c r="A17" s="11" t="inlineStr">
@@ -3777,7 +3781,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -3786,7 +3790,11 @@
         </is>
       </c>
       <c r="I17" s="11" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27.6" customHeight="1" s="19">
       <c r="A18" s="11" t="inlineStr">
@@ -3819,7 +3827,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -3828,7 +3836,11 @@
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55.15" customHeight="1" s="19">
       <c r="A19" s="11" t="inlineStr">
@@ -4317,7 +4329,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -4326,7 +4338,11 @@
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
-      <c r="J29" s="12" t="n"/>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="41.45" customHeight="1" s="19">
       <c r="A30" s="11" t="inlineStr">
@@ -4359,7 +4375,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -4368,7 +4384,11 @@
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
-      <c r="J30" s="12" t="n"/>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="27.6" customHeight="1" s="19">
       <c r="A31" s="11" t="inlineStr">
@@ -4401,7 +4421,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -4410,7 +4430,11 @@
         </is>
       </c>
       <c r="I31" s="11" t="n"/>
-      <c r="J31" s="12" t="n"/>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="27.6" customHeight="1" s="19">
       <c r="A32" s="11" t="inlineStr">
@@ -5109,7 +5133,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -5118,7 +5142,11 @@
         </is>
       </c>
       <c r="I46" s="11" t="n"/>
-      <c r="J46" s="12" t="n"/>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="41.45" customHeight="1" s="19">
       <c r="A47" s="11" t="inlineStr">
@@ -5151,7 +5179,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -5160,7 +5188,11 @@
         </is>
       </c>
       <c r="I47" s="11" t="n"/>
-      <c r="J47" s="12" t="n"/>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="27.6" customHeight="1" s="19">
       <c r="A48" s="11" t="inlineStr">
@@ -5193,7 +5225,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -5202,7 +5234,11 @@
         </is>
       </c>
       <c r="I48" s="11" t="n"/>
-      <c r="J48" s="12" t="n"/>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="27.6" customHeight="1" s="19">
       <c r="A49" s="11" t="inlineStr">
@@ -5235,7 +5271,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -5244,7 +5280,11 @@
         </is>
       </c>
       <c r="I49" s="11" t="n"/>
-      <c r="J49" s="12" t="n"/>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27.6" customHeight="1" s="19">
       <c r="A50" s="11" t="inlineStr">
@@ -5277,7 +5317,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -5286,7 +5326,11 @@
         </is>
       </c>
       <c r="I50" s="11" t="n"/>
-      <c r="J50" s="12" t="n"/>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55.15" customHeight="1" s="19">
       <c r="A51" s="11" t="inlineStr">
@@ -5319,7 +5363,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -5328,7 +5372,11 @@
         </is>
       </c>
       <c r="I51" s="11" t="n"/>
-      <c r="J51" s="12" t="n"/>
+      <c r="J51" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="41.45" customHeight="1" s="19">
       <c r="A52" s="11" t="inlineStr">
@@ -5361,7 +5409,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -5370,7 +5418,11 @@
         </is>
       </c>
       <c r="I52" s="11" t="n"/>
-      <c r="J52" s="12" t="n"/>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="41.45" customHeight="1" s="19">
       <c r="A53" s="11" t="inlineStr">
@@ -5403,7 +5455,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -5412,7 +5464,11 @@
         </is>
       </c>
       <c r="I53" s="11" t="n"/>
-      <c r="J53" s="12" t="n"/>
+      <c r="J53" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="27.6" customHeight="1" s="19">
       <c r="A54" s="11" t="inlineStr">
@@ -5445,7 +5501,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -5454,7 +5510,11 @@
         </is>
       </c>
       <c r="I54" s="11" t="n"/>
-      <c r="J54" s="12" t="n"/>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="41.45" customHeight="1" s="19">
       <c r="A55" s="11" t="inlineStr">
@@ -5487,7 +5547,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -5496,7 +5556,11 @@
         </is>
       </c>
       <c r="I55" s="11" t="n"/>
-      <c r="J55" s="12" t="n"/>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="41.45" customHeight="1" s="19">
       <c r="A56" s="11" t="inlineStr">
@@ -5534,13 +5598,13 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>HU-082 (actividades) es de Catalina y no está en el repo: sin actividades no hay casos que ejecutar.</t>
+          <t>HU-082 (actividades) es de Catalina y no está en el repo: sin actividades no hay casos que ejecutar.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
         </is>
       </c>
     </row>
@@ -5580,13 +5644,13 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-082.</t>
+          <t>Espera HU-082.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
         </is>
       </c>
     </row>
@@ -5626,13 +5690,13 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-082 y a la PO.</t>
+          <t>Espera HU-082 y a la PO.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7125,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -7070,7 +7134,11 @@
         </is>
       </c>
       <c r="I90" s="11" t="n"/>
-      <c r="J90" s="12" t="n"/>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="27.6" customHeight="1" s="19">
       <c r="A91" s="11" t="inlineStr">
@@ -7103,7 +7171,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -7112,7 +7180,11 @@
         </is>
       </c>
       <c r="I91" s="11" t="n"/>
-      <c r="J91" s="12" t="n"/>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="27.6" customHeight="1" s="19">
       <c r="A92" s="11" t="inlineStr">
@@ -9689,7 +9761,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
@@ -9698,7 +9770,11 @@
         </is>
       </c>
       <c r="I148" s="11" t="n"/>
-      <c r="J148" s="12" t="n"/>
+      <c r="J148" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="41.45" customHeight="1" s="19">
       <c r="A149" s="11" t="inlineStr">
@@ -9731,7 +9807,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -9740,7 +9816,11 @@
         </is>
       </c>
       <c r="I149" s="11" t="n"/>
-      <c r="J149" s="12" t="n"/>
+      <c r="J149" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="41.45" customHeight="1" s="19">
       <c r="A150" s="11" t="inlineStr">
@@ -9773,7 +9853,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
@@ -9782,7 +9862,11 @@
         </is>
       </c>
       <c r="I150" s="11" t="n"/>
-      <c r="J150" s="12" t="n"/>
+      <c r="J150" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="27.6" customHeight="1" s="19">
       <c r="A151" s="11" t="inlineStr">
@@ -9815,7 +9899,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -9824,7 +9908,11 @@
         </is>
       </c>
       <c r="I151" s="11" t="n"/>
-      <c r="J151" s="12" t="n"/>
+      <c r="J151" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="27.6" customHeight="1" s="19">
       <c r="A152" s="11" t="inlineStr">
@@ -9857,7 +9945,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -9866,7 +9954,11 @@
         </is>
       </c>
       <c r="I152" s="11" t="n"/>
-      <c r="J152" s="12" t="n"/>
+      <c r="J152" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="27.6" customHeight="1" s="19">
       <c r="A153" s="11" t="inlineStr">
@@ -9899,7 +9991,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -9908,7 +10000,11 @@
         </is>
       </c>
       <c r="I153" s="11" t="n"/>
-      <c r="J153" s="12" t="n"/>
+      <c r="J153" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="55.15" customHeight="1" s="19">
       <c r="A154" s="11" t="inlineStr">
@@ -9941,7 +10037,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -9950,7 +10046,11 @@
         </is>
       </c>
       <c r="I154" s="11" t="n"/>
-      <c r="J154" s="12" t="n"/>
+      <c r="J154" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="41.45" customHeight="1" s="19">
       <c r="A155" s="11" t="inlineStr">
@@ -9983,7 +10083,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
@@ -9992,7 +10092,11 @@
         </is>
       </c>
       <c r="I155" s="11" t="n"/>
-      <c r="J155" s="12" t="n"/>
+      <c r="J155" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="41.45" customHeight="1" s="19">
       <c r="A156" s="11" t="inlineStr">
@@ -11259,7 +11363,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H183" s="11" t="inlineStr">
@@ -11268,7 +11372,11 @@
         </is>
       </c>
       <c r="I183" s="11" t="n"/>
-      <c r="J183" s="12" t="n"/>
+      <c r="J183" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="41.45" customHeight="1" s="19">
       <c r="A184" s="11" t="inlineStr">
@@ -11301,7 +11409,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H184" s="11" t="inlineStr">
@@ -11310,7 +11418,11 @@
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
-      <c r="J184" s="12" t="n"/>
+      <c r="J184" s="12" t="inlineStr">
+        <is>
+          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="27.6" customHeight="1" s="19">
       <c r="A185" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2997,7 +2997,7 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>BD (modelo+SEL/INS/UPD/DEL+datos), Web (listado+ficha+menú) y Seguridad terminadas (Emilio). Pendiente pruebas/documentación.</t>
+          <t xml:space="preserve">BD (modelo+SEL/INS/UPD/DEL+datos), Web (listado+ficha+menú) y Seguridad terminadas (Emilio). Combo Categoría agregado a la ficha de tarea y pruebas/documentación cerradas por Catalina (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14854,11 +14854,15 @@
       </c>
       <c r="H264" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I264" s="11" t="n"/>
-      <c r="J264" s="12" t="n"/>
+      <c r="J264" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación) — 24-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="41.45" customHeight="1" s="19">
       <c r="A265" s="11" t="inlineStr">
@@ -14896,11 +14900,15 @@
       </c>
       <c r="H265" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I265" s="11" t="n"/>
-      <c r="J265" s="12" t="n"/>
+      <c r="J265" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación) — 24-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="27.6" customHeight="1" s="19">
       <c r="A266" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2776,7 +2776,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -2784,7 +2784,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P25" s="14" t="n"/>
+      <c r="P25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centro de tarea, listado, menú y seguridad ya integrados; combo Categoría agregado en esta iteración. Pruebas (CA-1 y CA-2) y documentación ejecutadas y cerradas por Catalina (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="69" customHeight="1" s="19">
       <c r="A26" s="11" t="inlineStr">
@@ -13098,11 +13102,15 @@
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I224" s="11" t="n"/>
-      <c r="J224" s="12" t="n"/>
+      <c r="J224" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="41.45" customHeight="1" s="19">
       <c r="A225" s="11" t="inlineStr">
@@ -13140,11 +13148,15 @@
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I225" s="11" t="n"/>
-      <c r="J225" s="12" t="n"/>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="41.45" customHeight="1" s="19">
       <c r="A226" s="11" t="inlineStr">
@@ -13182,11 +13194,15 @@
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I226" s="11" t="n"/>
-      <c r="J226" s="12" t="n"/>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="27.6" customHeight="1" s="19">
       <c r="A227" s="11" t="inlineStr">
@@ -13224,11 +13240,15 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I227" s="11" t="n"/>
-      <c r="J227" s="12" t="n"/>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="27.6" customHeight="1" s="19">
       <c r="A228" s="11" t="inlineStr">
@@ -13266,11 +13286,15 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I228" s="11" t="n"/>
-      <c r="J228" s="12" t="n"/>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="41.45" customHeight="1" s="19">
       <c r="A229" s="11" t="inlineStr">
@@ -13308,11 +13332,15 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I229" s="11" t="n"/>
-      <c r="J229" s="12" t="n"/>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27.6" customHeight="1" s="19">
       <c r="A230" s="11" t="inlineStr">
@@ -13350,11 +13378,15 @@
       </c>
       <c r="H230" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I230" s="11" t="n"/>
-      <c r="J230" s="12" t="n"/>
+      <c r="J230" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="27.6" customHeight="1" s="19">
       <c r="A231" s="11" t="inlineStr">
@@ -13392,11 +13424,15 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I231" s="11" t="n"/>
-      <c r="J231" s="12" t="n"/>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="27.6" customHeight="1" s="19">
       <c r="A232" s="11" t="inlineStr">
@@ -13434,11 +13470,15 @@
       </c>
       <c r="H232" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I232" s="11" t="n"/>
-      <c r="J232" s="12" t="n"/>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="41.45" customHeight="1" s="19">
       <c r="A233" s="11" t="inlineStr">
@@ -13476,11 +13516,15 @@
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I233" s="11" t="n"/>
-      <c r="J233" s="12" t="n"/>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="41.45" customHeight="1" s="19">
       <c r="A234" s="11" t="inlineStr">
@@ -13518,11 +13562,15 @@
       </c>
       <c r="H234" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
-      <c r="J234" s="12" t="n"/>
+      <c r="J234" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="27.6" customHeight="1" s="19">
       <c r="A235" s="11" t="inlineStr">
@@ -13560,11 +13608,15 @@
       </c>
       <c r="H235" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
-      <c r="J235" s="12" t="n"/>
+      <c r="J235" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="27.6" customHeight="1" s="19">
       <c r="A236" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2851,7 +2851,7 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t xml:space="preserve">Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1 y CA-2: fecha única con cuatro fechas -&gt; cuatro ocurrencias) y documentación ejecutadas y cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -14018,11 +14018,15 @@
       </c>
       <c r="H244" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I244" s="11" t="n"/>
-      <c r="J244" s="12" t="n"/>
+      <c r="J244" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="27.6" customHeight="1" s="19">
       <c r="A245" s="11" t="inlineStr">
@@ -14060,11 +14064,15 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I245" s="11" t="n"/>
-      <c r="J245" s="12" t="n"/>
+      <c r="J245" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="27.6" customHeight="1" s="19">
       <c r="A246" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -3076,7 +3076,7 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t xml:space="preserve">Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1 comentario con nombre/fecha e inmutable; CA-2 respuesta anidada) y documentación (endpoint API en Swagger + MD) cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -15558,11 +15558,15 @@
       </c>
       <c r="H278" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I278" s="11" t="n"/>
-      <c r="J278" s="12" t="n"/>
+      <c r="J278" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="41.45" customHeight="1" s="19">
       <c r="A279" s="11" t="inlineStr">
@@ -15600,11 +15604,15 @@
       </c>
       <c r="H279" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I279" s="11" t="n"/>
-      <c r="J279" s="12" t="n"/>
+      <c r="J279" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="27.6" customHeight="1" s="19"/>
     <row r="281" ht="27.6" customHeight="1" s="19"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1580,17 +1580,17 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="P9" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc/PO) bloqueadas hasta que exista el desarrollo.</t>
+          <t>Construida y probada por Bryan Chávez el 25-09-2026 (BD/289, BD/290, BD/291). Los cuatro criterios verificados de punta a punta: la actividad llega a la orden como paso, con su repuesto como cantidad planificada y la marca de permiso. La marcación de «no aplica» en terreno es de la app y se entrega en el Sprint 6. Pendiente la validación de la PO (T-4066).</t>
         </is>
       </c>
     </row>
@@ -5138,13 +5138,15 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/289. Revision: la tabla ya tenia sus 3 FK y el indice unico UX_PAA_HITO_CODIGO (codigo unico por HITO, no por cliente: el codigo se repite entre hitos a proposito).</t>
         </is>
       </c>
     </row>
@@ -5184,13 +5186,15 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/289. SEL_PLAN_ACTIVIDAD con @SELECT/@FROM/@WHERE y @FILTRO escapado; filtra por cliente cruzando el plan porque la actividad esta tres tablas mas abajo. Sirve a la grilla y a la ficha.</t>
         </is>
       </c>
     </row>
@@ -5230,13 +5234,15 @@
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I48" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/289. Valida antes de abrir transaccion: codigo unico por hito, procedimiento del mismo cliente, duracion &gt; 0, permiso con tipo, y NADA sobre version publicada. El orden se asigna solo al final del hito.</t>
         </is>
       </c>
     </row>
@@ -5276,13 +5282,15 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/289. ISNULL(@X, columna) mas @QUITA_PROCEDIMIENTO, @QUITA_PERMISO_TIPO y @QUITA_DURACION: sin esa ultima, vaciar la duracion y guardar dejaba la vieja. Descripcion vacia se guarda como NULL.</t>
         </is>
       </c>
     </row>
@@ -5322,13 +5330,15 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/289. Baja logica; rechaza si la actividad ya fue copiada en un paso de orden de trabajo (Orden_Trabajo_Paso.otp_plan_mantenimiento_actividad).</t>
         </is>
       </c>
     </row>
@@ -5368,13 +5378,15 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>_SEMILLA_PLAN_ACTIVIDADES.sql: 15 actividades en 4 hitos -uno en borrador para probar la escritura y tres publicados para ver la pantalla llena-, con permisos, parada y procedimiento enganchado.</t>
         </is>
       </c>
     </row>
@@ -5414,13 +5426,15 @@
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>PlanActividades.aspx. Se entra DESDE el hito (centro del plan &gt; Hitos &gt; Ver las N actividades), con el hito en el query cifrado; la columna HITO se esconde cuando hay uno elegido. Columna EXIGE con obligatoria / parada / permiso, y aviso de solo lectura si la version no es borrador.</t>
         </is>
       </c>
     </row>
@@ -5460,13 +5474,15 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>PlanActividad.aspx en modal con las clases sigma-modal-*. Incluye la lista de repuestos planificados (BD/291), que es el criterio 3 de la historia y no tenia camino de escritura.</t>
         </is>
       </c>
     </row>
@@ -5506,13 +5522,15 @@
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I54" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/290. Las dos filas en Menus (invisibles, permiso 116, bajo Planificacion) MAS sus Menu_Funcion con permiso 117: sin las funciones, PuedeFuncion devuelve false y la barra con Nueva/Eliminar no se dibuja para nadie.</t>
         </is>
       </c>
     </row>
@@ -5552,13 +5570,15 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Token.ExigirPagina por el master; Token.Puede("CREAR EDITAR PLANES MANTENIMIENTO") en el servidor al guardar, al eliminar y al tocar repuestos -no solo escondiendo el boton-; y Session.ClienteId() en cada consulta.</t>
         </is>
       </c>
     </row>
@@ -5598,13 +5618,15 @@
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>HU-082 (actividades) es de Catalina y no está en el repo: sin actividades no hay casos que ejecutar.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
+          <t>12 casos ejecutados con Selenium (capturas hu082_* y hu082b_* en Fase 2/Pruebas/capturas/S4). Los cuatro criterios se probaron de punta a punta: publicar la version, generar ocurrencias, generar la orden y mirarla.</t>
         </is>
       </c>
     </row>
@@ -5644,13 +5666,15 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I57" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-082.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md: bitacora del 25-09 y cuatro trampas nuevas en la seccion 7. Swagger no aplica: la pantalla es web y no hay endpoint de API para actividades de plan (misma decision pendiente que las otras 6 tareas de Swagger).</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16219,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16227,7 +16251,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16258,7 +16282,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16314,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2255,17 +2255,17 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) terminadas sobre el calendario del plan y generar OT (BD/216, BD/220). La bandeja global es de Catalina.</t>
+          <t>Construida y probada por Bryan Chávez el 26-09-2026 (BD/292, BD/293). Bandeja global con las cuatro situaciones, contadores que filtran, exportación y generación de la orden sobre lo seleccionado. La situación se deriva al consultar. Pendiente la validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -9882,13 +9882,15 @@
       </c>
       <c r="H150" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I150" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I150" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J150" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/292. Revision: Plan_Mantenimiento_Ocurrencia no tiene codigo -no es algo que alguien nombre-, asi que el "indice unico del codigo" de la plantilla no aplica; la hacen unica UX_PMO_HITO_ACTIVO_FECHA, UX_PMO_PROGRAMACION_ACTIVO_FECHA y UX_PMO_UUID. Ya estaba revisado en el bloque 216 y no cambio desde entonces.</t>
         </is>
       </c>
     </row>
@@ -9928,13 +9930,15 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J151" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/292. SEL_PLAN_OCURRENCIA_BANDEJA: todo por parametros, sin SQL armado. CTE para poder FILTRAR por la situacion, que es derivada; segundo result set con los contadores de TODO lo que cumple el filtro -no de la pagina- y sin aplicarse la situacion a si mismos, para poder salir del filtro. Mas RPT_..._EXCEL con el patron de RPT_PLAN_CALENDARIO_EXCEL.</t>
         </is>
       </c>
     </row>
@@ -9974,13 +9978,15 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J152" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/292. IX_PMO_ABIERTAS, indice FILTRADO por los estados abiertos: los que ya estaban parten por estado o traen todo el rango del cliente, y las cerradas se acumulan para siempre mientras las abiertas no, asi que ese recorrido crecia sin que creciera lo buscado.</t>
         </is>
       </c>
     </row>
@@ -10020,13 +10026,15 @@
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I153" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J153" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>_SEMILLA_BANDEJA_DISPONIBLES.sql. Tres de las cuatro situaciones ya salian de los datos; DISPONIBLE no aparece nunca porque dura solo la ventana de tolerancia. La semilla abre esa ventana en dos ocurrencias futuras -no les cambia la fecha programada- para poder verificar el criterio 1 completo.</t>
         </is>
       </c>
     </row>
@@ -10066,13 +10074,15 @@
       </c>
       <c r="H154" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I154" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I154" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="J154" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>PlanOcurrenciaBandeja.aspx. Los contadores son la botonera: cada uno filtra por su situacion. Se le dejo "Generar ordenes de trabajo" sobre lo seleccionado -el criterio 3 de la historia- y "Descargar Excel" con el mismo filtro que la grilla. Un hito sin actividades se avisa en la fila, antes de generar.</t>
         </is>
       </c>
     </row>
@@ -10112,13 +10122,15 @@
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J155" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>BD/293 la registra en Menus (visible, permiso 116, bajo Planificacion). Generar la orden pregunta en el servidor por "CREAR ORDEN TRABAJO" -no solo escondiendo el boton- y Session.ClienteId() va en cada consulta.</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10178,7 @@
       </c>
       <c r="J156" s="12" t="inlineStr">
         <is>
-          <t>Casos ejecutados sobre SEL_PLAN_CALENDARIO (situación derivada) y generar OT desde la ocurrencia. La bandeja global es de Catalina.</t>
+          <t>3 casos ejecutados con Selenium sobre la bandeja misma (capturas hu087_* y hu087c_* en Fase 2/Pruebas/capturas/S4): las cuatro situaciones con sus contadores, el filtro por situacion derivada, y generar la orden desde la bandeja con la ocurrencia quedando enlazada.</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10226,7 @@
       </c>
       <c r="J157" s="12" t="inlineStr">
         <is>
-          <t>GET/POST /plan-ocurrencias documentados en XML del controlador; MD 10.5.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md: bitacora del 26-09 con por que la bandeja es un SP propio y no un parametro mas del calendario. Swagger no aplica: es pantalla web, sin endpoint de API.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>BD (SP reprogramar+SEL+datos), Web PlanOcurrenciaReprogramar.aspx y Seguridad terminadas (Emilio). Pendiente pruebas/documentación.</t>
+          <t>Construida por Emilio Fuentes (bloque 202). Al cerrarla el 26-09-2026 se encontró que la pantalla de reprogramar no tenía entrada desde ningún lado y que el indicador de cumplimiento del criterio 2 no existía: Bryan Chávez le dio entrada desde la bandeja, escribió SEL_PLAN_CUMPLIMIENTO (BD/294) y corrigió tres defectos que nunca se habían ejecutado (BD/295 y la ficha). Los tres criterios verificados. Pendiente la validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -3740,13 +3740,15 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Casos ejecutados con Selenium sobre HU-080: alta de plan con su version 1 en borrador, codigo unico por cliente, y plan acotado a un tipo que solo ofrece equipos de ese tipo. Capturas hu080_* en Fase 2/Pruebas/capturas/S4.</t>
         </is>
       </c>
     </row>
@@ -3786,13 +3788,15 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md, bitacora del 26-09. Swagger no aplica: el plan es pantalla web y no hay endpoint de API.</t>
         </is>
       </c>
     </row>
@@ -4334,13 +4338,15 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Casos de HU-081: alta de hito con programacion, hito sin programacion rechazado, un hito con varias actividades genera UNA orden con un paso por actividad, y overhaul con parada llega marcado a la ocurrencia y a la orden. Capturas hu081_* y t3_hu081_* .</t>
         </is>
       </c>
     </row>
@@ -4380,13 +4386,15 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md, bitacora del 26-09. Swagger no aplica.</t>
         </is>
       </c>
     </row>
@@ -7154,13 +7162,15 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Casos de HU-083, incluido el #3 que estaba sin construir: el aviso de que el equipo ya esta en otro plan vigente. Se construyo (BD/294, SEL_PLAN_ACTIVO_COBERTURA + el panel en la ficha del equipo) porque escribir un caso de prueba sobre algo que no existe no lo hace existir. Horas sobre lo estimado por esa razon.</t>
         </is>
       </c>
     </row>
@@ -7200,13 +7210,15 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J91" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md, bitacora del 26-09.</t>
         </is>
       </c>
     </row>
@@ -9790,13 +9802,15 @@
       </c>
       <c r="H148" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I148" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I148" s="11" t="n">
+        <v>2</v>
+      </c>
       <c r="J148" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Casos de HU-086. Los tres criterios estaban sin verificar y dos sin construir: la pantalla de reprogramar existia desde el bloque 202 y NINGUN lugar la abria -escrita y muerta-, y el indicador de cumplimiento no existia. Se le dio entrada desde la bandeja y se escribio SEL_PLAN_CUMPLIMIENTO (BD/294). Ademas se corrigio PLAN_OCURRENCIA_REPROGRAMAR (BD/295): copiaba la ventana de tolerancia sin moverla, asi que reprogramar mas alla de la tolerancia reventaba contra CK_PMO_LIMITE y, cuando no reventaba, la ocurrencia nueva nacia ya vencida.</t>
         </is>
       </c>
     </row>
@@ -9836,13 +9850,15 @@
       </c>
       <c r="H149" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I149" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I149" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J149" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md, bitacora del 26-09, con el defecto de la ventana de tolerancia y por que el cumplimiento se mide contra la fecha original.</t>
         </is>
       </c>
     </row>
@@ -11404,13 +11420,15 @@
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I183" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J183" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Casos de HU-085: calendario anual con su distribucion por mes, filtro de trabajos con parada y carga estimada por semana. Capturas hu085_* .</t>
         </is>
       </c>
     </row>
@@ -11450,13 +11468,15 @@
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I184" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J184" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>MD/SIGMA_ESTADO_DESARROLLO.md, bitacora del 26-09.</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16026,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16662,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17187,7 +17207,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17238,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17249,7 +17269,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1885,12 +1885,12 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) terminadas: publicar y abrir versión nueva desde el centro del plan (BD/219). Estado de la historia lo cierra Emilio.</t>
+          <t>Construida por Emilio Fuentes; reasignada a Bryan Chávez el 27-09-2026. Los 5 criterios verificados: el #4 (publicación simultánea) se probó con dos sesiones SQL a la vez — una publica y la otra, bloqueada hasta el commit de la primera, recibe «La versión ya no está en borrador» (BD/301 unificó ese mensaje; antes decía «Solo se publica una versión en borrador»). Evidencia hu084_4_carrera.txt en Fase 2/Pruebas/capturas/S4. Pendiente validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · Estado corregido el 27-09-2026: la historia ya se había movido al Sprint 6 en la Sprint Review 1 y seguía figurando En revisión.</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio. · Estado corregido el 27-09-2026: la historia ya se había movido al Sprint 6 en la Sprint Review 1 y seguía figurando En revisión.</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -2784,7 +2784,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P25" s="14" t="n"/>
+      <c r="P25" s="14" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: el desarrollo ya existía (hecho con HU-102). Quedan sus pruebas y documentación (T-4281, T-4282) y los 2 criterios por verificar.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="69" customHeight="1" s="19">
       <c r="A26" s="11" t="inlineStr">
@@ -7584,11 +7588,11 @@
         </is>
       </c>
       <c r="I99" s="11" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>Faltaba abrir la versión siguiente: BD/219 (INS_PLAN_VERSION_NUEVA copia hitos/actividades/equipos; UPD_PLAN_VERSION_PUBLICAR). Casos en MD 10.8.</t>
+          <t>Faltaba abrir la versión siguiente: BD/219 (INS_PLAN_VERSION_NUEVA copia hitos/actividades/equipos; UPD_PLAN_VERSION_PUBLICAR). Casos en MD 10.8. · 27-09-2026: criterio #4 verificado con dos sesiones sqlcmd simultáneas sobre PMA-2 v2 (A publica y retiene el bloqueo 6 s; B espera y es rechazada con «La versión ya no está en borrador»). Datos restaurados. BD/301 corrige el mensaje. +0,75 h.</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7640,7 @@
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>MD/SIGMA_CHECKLIST_PENDIENTES.md 10.8. Sin endpoint propio: la publicación es web.</t>
+          <t>MD/SIGMA_CHECKLIST_PENDIENTES.md 10.8. Sin endpoint propio: la publicación es web. · 27-09-2026: MD/SIGMA_ESTADO_DESARROLLO.md, bitácora — cómo se decide la carrera de publicación y por qué cambió el mensaje (BD/301).</t>
         </is>
       </c>
     </row>
@@ -8091,18 +8095,18 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>HU-091 (umbrales) la construye Catalina; sus tareas no están en el repo.</t>
+          <t>HU-091 (umbrales) la construye Catalina; sus tareas no están en el repo. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
         </is>
       </c>
     </row>
@@ -8137,18 +8141,18 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-091 (Catalina).</t>
+          <t>Espera HU-091 (Catalina). · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
         </is>
       </c>
     </row>
@@ -8183,18 +8187,18 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-091 (Catalina) y a la PO.</t>
+          <t>Espera HU-091 (Catalina) y a la PO. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
         </is>
       </c>
     </row>
@@ -10604,13 +10608,13 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I165" s="11" t="n"/>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>HU-093 (publicar plantilla) es de Emilio; espera su merge.</t>
+          <t>HU-093 (publicar plantilla) es de Emilio; espera su merge. · Desbloqueada el 27-09-2026: el desarrollo ya existe (ChecklistVersion.aspx + PUBLICAR_CHECKLIST_VERSION).</t>
         </is>
       </c>
     </row>
@@ -10650,13 +10654,13 @@
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I166" s="11" t="n"/>
       <c r="J166" s="12" t="inlineStr">
         <is>
-          <t>Espera merge de Emilio.</t>
+          <t>Espera merge de Emilio. · Desbloqueada el 27-09-2026: el desarrollo ya existe (ChecklistVersion.aspx + PUBLICAR_CHECKLIST_VERSION).</t>
         </is>
       </c>
     </row>
@@ -12344,13 +12348,13 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
       <c r="J203" s="12" t="inlineStr">
         <is>
-          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · Movida al Sprint 6 el 27-09-2026 junto con su historia (app móvil).</t>
         </is>
       </c>
     </row>
@@ -12390,13 +12394,13 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
       <c r="J204" s="12" t="inlineStr">
         <is>
-          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · Movida al Sprint 6 el 27-09-2026 junto con su historia (app móvil).</t>
         </is>
       </c>
     </row>
@@ -12436,13 +12440,13 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. · Movida al Sprint 6 el 27-09-2026 junto con su historia (app móvil).</t>
         </is>
       </c>
     </row>
@@ -13266,11 +13270,17 @@
       </c>
       <c r="H224" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I224" s="11" t="n"/>
-      <c r="J224" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I224" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Modelo Tarea revisado: PK_TAREA y UX_TAR_CLIENTE_CODIGO (código único por cliente). Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="41.45" customHeight="1" s="19">
       <c r="A225" s="11" t="inlineStr">
@@ -13308,11 +13318,17 @@
       </c>
       <c r="H225" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I225" s="11" t="n"/>
-      <c r="J225" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I225" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). SEL_TAREA existe (BD/218). Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="41.45" customHeight="1" s="19">
       <c r="A226" s="11" t="inlineStr">
@@ -13350,11 +13366,17 @@
       </c>
       <c r="H226" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I226" s="11" t="n"/>
-      <c r="J226" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I226" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). INS_TAREA existe (BD/218), con código TAR- automático. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="27.6" customHeight="1" s="19">
       <c r="A227" s="11" t="inlineStr">
@@ -13392,11 +13414,17 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I227" s="11" t="n"/>
-      <c r="J227" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). UPD_TAREA existe (BD/218). Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="27.6" customHeight="1" s="19">
       <c r="A228" s="11" t="inlineStr">
@@ -13434,11 +13462,17 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="n"/>
-      <c r="J228" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). DEL_TAREA existe (BD/218), baja lógica. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="41.45" customHeight="1" s="19">
       <c r="A229" s="11" t="inlineStr">
@@ -13476,11 +13510,17 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I229" s="11" t="n"/>
-      <c r="J229" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I229" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Datos de prueba: 7 tareas del cliente de pruebas, 5 asociadas a un equipo. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27.6" customHeight="1" s="19">
       <c r="A230" s="11" t="inlineStr">
@@ -13518,11 +13558,17 @@
       </c>
       <c r="H230" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I230" s="11" t="n"/>
-      <c r="J230" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Listado Tareas.aspx existe. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="27.6" customHeight="1" s="19">
       <c r="A231" s="11" t="inlineStr">
@@ -13560,11 +13606,17 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I231" s="11" t="n"/>
-      <c r="J231" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I231" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Ficha Tarea.aspx existe como centro de la tarea (Ficha, Programaciones, Ocurrencias, Evidencias, Comentarios), no como RadWindow. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="27.6" customHeight="1" s="19">
       <c r="A232" s="11" t="inlineStr">
@@ -13602,11 +13654,17 @@
       </c>
       <c r="H232" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I232" s="11" t="n"/>
-      <c r="J232" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I232" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Menus 2190 (Tareas recurrentes) y 2191 (Tarea, detalle) con permiso 118. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="41.45" customHeight="1" s="19">
       <c r="A233" s="11" t="inlineStr">
@@ -13644,11 +13702,17 @@
       </c>
       <c r="H233" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I233" s="11" t="n"/>
-      <c r="J233" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I233" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="12" t="inlineStr">
+        <is>
+          <t>Conciliada el 27-09-2026: ya estaba construido por Bryan Chávez junto con HU-102 (T-4283 a T-4293). Seguridad en el servidor con Token.Puede en Tarea.aspx.cs y el menú por permiso 118. Sin horas nuevas.</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="41.45" customHeight="1" s="19">
       <c r="A234" s="11" t="inlineStr">
@@ -14465,18 +14529,18 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H252" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t>HU-097 (historial de pauta) la construye Catalina; espera su desarrollo.</t>
+          <t>HU-097 (historial de pauta) la construye Catalina; espera su desarrollo. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
         </is>
       </c>
     </row>
@@ -14511,18 +14575,18 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I253" s="11" t="n"/>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-097 (Catalina).</t>
+          <t>Espera HU-097 (Catalina). · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16852,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1730,7 +1730,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t xml:space="preserve">Dev de la bandeja verificado por Bryan. Pruebas (CA-1 bandeja ordenada, CA-2 convertir en OT, CA-3 descartar con motivo) y documentación cerradas por Catalina (28-09-2026). Se corrigió el orden de la bandeja: por severidad y antigüedad, no solo por fecha.</t>
         </is>
       </c>
     </row>
@@ -6630,11 +6630,15 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
-      <c r="J78" s="12" t="n"/>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="41.45" customHeight="1" s="19">
       <c r="A79" s="11" t="inlineStr">
@@ -6672,11 +6676,15 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
-      <c r="J79" s="12" t="n"/>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27.6" customHeight="1" s="19">
       <c r="A80" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2405,7 +2405,7 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>Construida por Emilio Fuentes (22-09-2026): BD SEL/INS/UPD_CHECKLIST_PROGRAMACION (resuelve version publicada, exige activo O area, FNC_PAIS_HORA, patron dinamico) + datos de prueba (BD/197, 198). Web ChecklistProgramacions/ChecklistProgramacion con Model+Controller; combos por SEL_. Seguridad por cliente + Token. Compila exitcode=0; CA3 verificado en transaccion revertida. NOTA: para programar una pauta debe estar PUBLICADA (HU-093). PENDIENTE (Catalina): pruebas y documentacion.</t>
+          <t xml:space="preserve">CRUD de la programación verificado. FALTABA el generador de ocurrencias: se construyó GEN_CHECKLIST_OCURRENCIAS (BD/304) + botón «Generar ocurrencias». Pruebas (CA-1 activo, CA-2 área, CA-3 rechazo sin objetivo) y documentación cerradas por Catalina (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -11076,11 +11076,15 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
-      <c r="J175" s="12" t="n"/>
+      <c r="J175" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="27.6" customHeight="1" s="19">
       <c r="A176" s="11" t="inlineStr">
@@ -11118,11 +11122,15 @@
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
-      <c r="J176" s="12" t="n"/>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="27.6" customHeight="1" s="19">
       <c r="A177" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2926,7 +2926,7 @@
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O27" s="14" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) bloqueadas hasta que exista el desarrollo.</t>
+          <t xml:space="preserve">Desarrollo construido por Catalina: SP SEL_CHECKLIST_HISTORIAL + índice (BD/306), pantalla ChecklistHistorial.aspx (solo lectura) + GetHistorial, y permiso/menú VER HISTORIAL CHECKLIST (BD/305). El detalle reutiliza los SP de respuestas/archivos. Pruebas (CA-1, CA-2) y documentación cerradas (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14314,11 +14314,15 @@
       </c>
       <c r="H246" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I246" s="11" t="n"/>
-      <c r="J246" s="12" t="n"/>
+      <c r="J246" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="27.6" customHeight="1" s="19">
       <c r="A247" s="11" t="inlineStr">
@@ -14356,11 +14360,15 @@
       </c>
       <c r="H247" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I247" s="11" t="n"/>
-      <c r="J247" s="12" t="n"/>
+      <c r="J247" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="41.45" customHeight="1" s="19">
       <c r="A248" s="11" t="inlineStr">
@@ -14398,11 +14406,15 @@
       </c>
       <c r="H248" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I248" s="11" t="n"/>
-      <c r="J248" s="12" t="n"/>
+      <c r="J248" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="27.6" customHeight="1" s="19">
       <c r="A249" s="11" t="inlineStr">
@@ -14440,11 +14452,15 @@
       </c>
       <c r="H249" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I249" s="11" t="n"/>
-      <c r="J249" s="12" t="n"/>
+      <c r="J249" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="27.6" customHeight="1" s="19">
       <c r="A250" s="11" t="inlineStr">
@@ -14482,11 +14498,15 @@
       </c>
       <c r="H250" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I250" s="11" t="n"/>
-      <c r="J250" s="12" t="n"/>
+      <c r="J250" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="27.6" customHeight="1" s="19">
       <c r="A251" s="11" t="inlineStr">
@@ -14524,11 +14544,15 @@
       </c>
       <c r="H251" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I251" s="11" t="n"/>
-      <c r="J251" s="12" t="n"/>
+      <c r="J251" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="27.6" customHeight="1" s="19">
       <c r="A252" s="11" t="inlineStr">
@@ -14566,13 +14590,13 @@
       </c>
       <c r="H252" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t>HU-097 (historial de pauta) la construye Catalina; espera su desarrollo. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14612,13 +14636,13 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I253" s="11" t="n"/>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-097 (Catalina). · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc/PO) bloqueadas hasta que exista el desarrollo.</t>
+          <t xml:space="preserve">Mantenedor de umbrales/acciones construido por Catalina: SP SEL/INS/UPD/DEL_CHECKLIST_ITEM_VALIDACION (BD/307), pantallas ChecklistItemValidacion(s) + controller/modelo, permisos/menú (BD/308). Pruebas (CA-1: 84-&gt;crítica; CA-2/3/4 definición+runtime) y documentación cerradas (29-09-2026). Pendiente solo la validación funcional con la PO (T-4137).</t>
         </is>
       </c>
     </row>
@@ -7688,11 +7688,15 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I101" s="11" t="n"/>
-      <c r="J101" s="12" t="n"/>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="41.45" customHeight="1" s="19">
       <c r="A102" s="11" t="inlineStr">
@@ -7730,11 +7734,15 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
-      <c r="J102" s="12" t="n"/>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="27.6" customHeight="1" s="19">
       <c r="A103" s="11" t="inlineStr">
@@ -7772,11 +7780,15 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I103" s="11" t="n"/>
-      <c r="J103" s="12" t="n"/>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="27.6" customHeight="1" s="19">
       <c r="A104" s="11" t="inlineStr">
@@ -7814,11 +7826,15 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
-      <c r="J104" s="12" t="n"/>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="27.6" customHeight="1" s="19">
       <c r="A105" s="11" t="inlineStr">
@@ -7856,11 +7872,15 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
-      <c r="J105" s="12" t="n"/>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="27.6" customHeight="1" s="19">
       <c r="A106" s="11" t="inlineStr">
@@ -7898,11 +7918,15 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
-      <c r="J106" s="12" t="n"/>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="27.6" customHeight="1" s="19">
       <c r="A107" s="11" t="inlineStr">
@@ -7940,11 +7964,15 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
-      <c r="J107" s="12" t="n"/>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="27.6" customHeight="1" s="19">
       <c r="A108" s="11" t="inlineStr">
@@ -7982,11 +8010,15 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
-      <c r="J108" s="12" t="n"/>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="27.6" customHeight="1" s="19">
       <c r="A109" s="11" t="inlineStr">
@@ -8024,11 +8056,15 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
-      <c r="J109" s="12" t="n"/>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="27.6" customHeight="1" s="19">
       <c r="A110" s="11" t="inlineStr">
@@ -8066,11 +8102,15 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I110" s="11" t="n"/>
-      <c r="J110" s="12" t="n"/>
+      <c r="J110" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="27.6" customHeight="1" s="19">
       <c r="A111" s="11" t="inlineStr">
@@ -8108,13 +8148,13 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t>HU-091 (umbrales) la construye Catalina; sus tareas no están en el repo. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8154,13 +8194,13 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-091 (Catalina). · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -2705,7 +2705,7 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -2713,7 +2713,11 @@
           <t>Catalina Pescio</t>
         </is>
       </c>
-      <c r="P24" s="12" t="n"/>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenedor de dependencias entre ítems construido: BD SP SEL/INS/UPD/DEL (BD/309), Web listado+ficha+controlador+modelo y menú/permisos (BD/310). Pruebas y documentación cerradas por Catalina Pescio (29-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55.15" customHeight="1" s="19">
       <c r="A25" s="13" t="inlineStr">
@@ -12822,11 +12826,15 @@
       </c>
       <c r="H212" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
-      <c r="J212" s="12" t="n"/>
+      <c r="J212" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="27.6" customHeight="1" s="19">
       <c r="A213" s="11" t="inlineStr">
@@ -12864,11 +12872,15 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
-      <c r="J213" s="12" t="n"/>
+      <c r="J213" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="55.15" customHeight="1" s="19">
       <c r="A214" s="11" t="inlineStr">
@@ -12906,11 +12918,15 @@
       </c>
       <c r="H214" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
-      <c r="J214" s="12" t="n"/>
+      <c r="J214" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="41.45" customHeight="1" s="19">
       <c r="A215" s="11" t="inlineStr">
@@ -12948,11 +12964,15 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
-      <c r="J215" s="12" t="n"/>
+      <c r="J215" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="41.45" customHeight="1" s="19">
       <c r="A216" s="11" t="inlineStr">
@@ -12990,11 +13010,15 @@
       </c>
       <c r="H216" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I216" s="11" t="n"/>
-      <c r="J216" s="12" t="n"/>
+      <c r="J216" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="41.45" customHeight="1" s="19">
       <c r="A217" s="11" t="inlineStr">
@@ -13032,11 +13056,15 @@
       </c>
       <c r="H217" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I217" s="11" t="n"/>
-      <c r="J217" s="12" t="n"/>
+      <c r="J217" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="41.45" customHeight="1" s="19">
       <c r="A218" s="11" t="inlineStr">
@@ -13074,11 +13102,15 @@
       </c>
       <c r="H218" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I218" s="11" t="n"/>
-      <c r="J218" s="12" t="n"/>
+      <c r="J218" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="27.6" customHeight="1" s="19">
       <c r="A219" s="11" t="inlineStr">
@@ -13116,11 +13148,15 @@
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
-      <c r="J219" s="12" t="n"/>
+      <c r="J219" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="27.6" customHeight="1" s="19">
       <c r="A220" s="11" t="inlineStr">
@@ -13158,11 +13194,15 @@
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I220" s="11" t="n"/>
-      <c r="J220" s="12" t="n"/>
+      <c r="J220" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="27.6" customHeight="1" s="19">
       <c r="A221" s="11" t="inlineStr">
@@ -13200,11 +13240,15 @@
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I221" s="11" t="n"/>
-      <c r="J221" s="12" t="n"/>
+      <c r="J221" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="27.6" customHeight="1" s="19">
       <c r="A222" s="11" t="inlineStr">
@@ -13242,11 +13286,15 @@
       </c>
       <c r="H222" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I222" s="11" t="n"/>
-      <c r="J222" s="12" t="n"/>
+      <c r="J222" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="27.6" customHeight="1" s="19">
       <c r="A223" s="11" t="inlineStr">
@@ -13284,11 +13332,15 @@
       </c>
       <c r="H223" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t xml:space="preserve">Terminada</t>
         </is>
       </c>
       <c r="I223" s="11" t="n"/>
-      <c r="J223" s="12" t="n"/>
+      <c r="J223" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="55.15" customHeight="1" s="19">
       <c r="A224" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1355,7 +1355,7 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -1655,17 +1655,17 @@
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>Construida por Emilio Fuentes (11-09-2026) siguiendo PATRONES/ASP: BD SEL/INS/UPD/DEL_CHECKLIST_PLANTILLA (patron dinamico, FNC_PAIS_HORA, INS_EXCEPCION, codigo unico por cliente, baja logica) + estructura Version/Seccion/Item/Validacion (BD/192) + lookups (BD/189,191,194). Web: ChecklistPlantillas/ChecklistPlantilla/ChecklistPlantillaVista con Model+Controllers; editor inline de secciones y campos; previsualizacion de solo lectura al clic. Datos reales: SOP-09-R24 con 25 secciones y 208 campos (BD/193). Seguridad por cliente + Token + Menu_Funcion. Compila exitcode=0 y SP probados en transaccion revertida. PENDIENTE (otra persona): pruebas por criterio, documentacion y consumo movil.</t>
+          <t>Construida por Emilio; las pruebas y la documentación las tomó Bryan. La prueba de CA1 destapó que la plantilla se creaba sin su versión 1 en borrador: corregido en BD/321.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dev de la bandeja verificado por Bryan. Pruebas (CA-1 bandeja ordenada, CA-2 convertir en OT, CA-3 descartar con motivo) y documentación cerradas por Catalina (28-09-2026). Se corrigió el orden de la bandeja: por severidad y antigüedad, no solo por fecha.</t>
+          <t>Dev de la bandeja verificado por Bryan. Pruebas (CA-1 bandeja ordenada, CA-2 convertir en OT, CA-3 descartar con motivo) y documentación cerradas por Catalina (28-09-2026). Se corrigió el orden de la bandeja: por severidad y antigüedad, no solo por fecha.</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenedor de umbrales/acciones construido por Catalina: SP SEL/INS/UPD/DEL_CHECKLIST_ITEM_VALIDACION (BD/307), pantallas ChecklistItemValidacion(s) + controller/modelo, permisos/menú (BD/308). Pruebas (CA-1: 84-&gt;crítica; CA-2/3/4 definición+runtime) y documentación cerradas (29-09-2026). Pendiente solo la validación funcional con la PO (T-4137).</t>
+          <t>Mantenedor de umbrales/acciones construido por Catalina: SP SEL/INS/UPD/DEL_CHECKLIST_ITEM_VALIDACION (BD/307), pantallas ChecklistItemValidacion(s) + controller/modelo, permisos/menú (BD/308). Pruebas (CA-1: 84-&gt;crítica; CA-2/3/4 definición+runtime) y documentación cerradas (29-09-2026). Pendiente solo la validación funcional con la PO (T-4137).</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>Tareas de Bryan (pruebas/doc) bloqueadas hasta que exista el desarrollo.</t>
+          <t>Pruebas ejecutadas el 01-10-2026: 4 casos, todos conformes.</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRUD de la programación verificado. FALTABA el generador de ocurrencias: se construyó GEN_CHECKLIST_OCURRENCIAS (BD/304) + botón «Generar ocurrencias». Pruebas (CA-1 activo, CA-2 área, CA-3 rechazo sin objetivo) y documentación cerradas por Catalina (28-09-2026).</t>
+          <t>CRUD de la programación verificado. FALTABA el generador de ocurrencias: se construyó GEN_CHECKLIST_OCURRENCIAS (BD/304) + botón «Generar ocurrencias». Pruebas (CA-1 activo, CA-2 área, CA-3 rechazo sin objetivo) y documentación cerradas por Catalina (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenedor de dependencias entre ítems construido: BD SP SEL/INS/UPD/DEL (BD/309), Web listado+ficha+controlador+modelo y menú/permisos (BD/310). Pruebas y documentación cerradas por Catalina Pescio (29-09-2026).</t>
+          <t>Mantenedor de dependencias entre ítems construido: BD SP SEL/INS/UPD/DEL (BD/309), Web listado+ficha+controlador+modelo y menú/permisos (BD/310). Pruebas y documentación cerradas por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centro de tarea, listado, menú y seguridad integrados; combo Categoría agregado. Pruebas (CA-1 y CA-2) y documentación cerradas por Catalina (24-09-2026).</t>
+          <t>Centro de tarea, listado, menú y seguridad integrados; combo Categoría agregado. Pruebas (CA-1 y CA-2) y documentación cerradas por Catalina (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="N26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1, CA-2: fecha única con cuatro fechas -&gt; cuatro ocurrencias) y documentación cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
+          <t>Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1, CA-2: fecha única con cuatro fechas -&gt; cuatro ocurrencias) y documentación cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O27" s="14" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Desarrollo construido por Catalina: SP SEL_CHECKLIST_HISTORIAL + índice (BD/306), pantalla ChecklistHistorial.aspx (solo lectura) + GetHistorial, y permiso/menú VER HISTORIAL CHECKLIST (BD/305). El detalle reutiliza los SP de respuestas/archivos. Pruebas (CA-1, CA-2) y documentación cerradas (29-09-2026).</t>
+          <t>Desarrollo construido por Catalina: SP SEL_CHECKLIST_HISTORIAL + índice (BD/306), pantalla ChecklistHistorial.aspx (solo lectura) + GetHistorial, y permiso/menú VER HISTORIAL CHECKLIST (BD/305). El detalle reutiliza los SP de respuestas/archivos. Pruebas (CA-1, CA-2) y documentación cerradas (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="N28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O28" s="12" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BD/Web/Seguridad terminadas (Emilio). Combo Categoría agregado a la ficha de tarea y pruebas/documentación cerradas por Catalina (24-09-2026).</t>
+          <t>BD/Web/Seguridad terminadas (Emilio). Combo Categoría agregado a la ficha de tarea y pruebas/documentación cerradas por Catalina (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1 inmutable con nombre/fecha; CA-2 respuesta anidada) y documentación (endpoint API en Swagger + MD) cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
+          <t>Hecho y verificado por Bryan (12-09-2026). Pruebas (CA-1 inmutable con nombre/fecha; CA-2 respuesta anidada) y documentación (endpoint API en Swagger + MD) cerradas por Catalina (24-09-2026). Pendiente solo validación de la PO.</t>
         </is>
       </c>
     </row>
@@ -3844,13 +3844,15 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Validación funcional con la Product Owner: conforme.</t>
         </is>
       </c>
     </row>
@@ -4442,13 +4444,15 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>Reasignada a Bryan Chávez (24-09-2026): continúa el épico del plan de mantenimiento.</t>
+          <t>Validación funcional con la Product Owner: conforme.</t>
         </is>
       </c>
     </row>
@@ -5730,13 +5734,15 @@
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-082 y a la PO.  Desbloqueada (24-09-2026): el desarrollo del que dependía pasa al mismo responsable.</t>
+          <t>Validación funcional con la Product Owner: conforme.</t>
         </is>
       </c>
     </row>
@@ -6231,16 +6237,22 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="n"/>
-      <c r="J69" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>Ejecutada el 01-10-2026: 4 casos sobre los criterios de HU-090, todos conformes.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="41.45" customHeight="1" s="19">
       <c r="A70" s="11" t="inlineStr">
@@ -6273,16 +6285,22 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>Documentado en el MD de estado: la plantilla nace con su version 1 en borrador (BD/321).</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="27.6" customHeight="1" s="19">
       <c r="A71" s="11" t="inlineStr">
@@ -6315,16 +6333,22 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I71" s="11" t="n"/>
-      <c r="J71" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>Validación funcional con la Product Owner: conforme.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="41.45" customHeight="1" s="19">
       <c r="A72" s="11" t="inlineStr">
@@ -6634,13 +6658,13 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -6680,13 +6704,13 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7692,13 +7716,13 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7738,13 +7762,13 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7784,13 +7808,13 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7830,13 +7854,13 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7876,13 +7900,13 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7922,13 +7946,13 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -7968,13 +7992,13 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8014,13 +8038,13 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8060,13 +8084,13 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8106,13 +8130,13 @@
       </c>
       <c r="H110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8152,13 +8176,13 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8198,13 +8222,13 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -8244,13 +8268,15 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I113" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J113" s="12" t="inlineStr">
         <is>
-          <t>Espera HU-091 (Catalina) y a la PO. · Desbloqueada el 27-09-2026: pasa a la dueña de la historia, que la construye (antes Bryan Chávez); así no espera a otra persona.</t>
+          <t>Validación funcional con la Product Owner: conforme.</t>
         </is>
       </c>
     </row>
@@ -10660,13 +10686,15 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I165" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I165" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J165" s="12" t="inlineStr">
         <is>
-          <t>HU-093 (publicar plantilla) es de Emilio; espera su merge. · Desbloqueada el 27-09-2026: el desarrollo ya existe (ChecklistVersion.aspx + PUBLICAR_CHECKLIST_VERSION).</t>
+          <t>Ejecutada el 01-10-2026: 4 casos sobre los criterios de HU-093, todos conformes.</t>
         </is>
       </c>
     </row>
@@ -10706,13 +10734,15 @@
       </c>
       <c r="H166" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I166" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I166" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J166" s="12" t="inlineStr">
         <is>
-          <t>Espera merge de Emilio. · Desbloqueada el 27-09-2026: el desarrollo ya existe (ChecklistVersion.aspx + PUBLICAR_CHECKLIST_VERSION).</t>
+          <t>Documentado en el MD de estado: publicacion, retiro de la anterior y reconstruccion historica.</t>
         </is>
       </c>
     </row>
@@ -11120,13 +11150,13 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
       <c r="J175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -11166,13 +11196,13 @@
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
       <c r="J176" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio (28-09-2026).</t>
         </is>
       </c>
     </row>
@@ -12826,13 +12856,13 @@
       </c>
       <c r="H212" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I212" s="11" t="n"/>
       <c r="J212" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -12872,13 +12902,13 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I213" s="11" t="n"/>
       <c r="J213" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -12918,13 +12948,13 @@
       </c>
       <c r="H214" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -12964,13 +12994,13 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I215" s="11" t="n"/>
       <c r="J215" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13010,13 +13040,13 @@
       </c>
       <c r="H216" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I216" s="11" t="n"/>
       <c r="J216" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13056,13 +13086,13 @@
       </c>
       <c r="H217" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I217" s="11" t="n"/>
       <c r="J217" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13102,13 +13132,13 @@
       </c>
       <c r="H218" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13148,13 +13178,13 @@
       </c>
       <c r="H219" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I219" s="11" t="n"/>
       <c r="J219" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13194,13 +13224,13 @@
       </c>
       <c r="H220" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I220" s="11" t="n"/>
       <c r="J220" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13240,13 +13270,13 @@
       </c>
       <c r="H221" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I221" s="11" t="n"/>
       <c r="J221" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada por Catalina Pescio — 29-09-2026.</t>
+          <t>Terminada por Catalina Pescio — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13286,13 +13316,13 @@
       </c>
       <c r="H222" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I222" s="11" t="n"/>
       <c r="J222" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
+          <t>Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13332,13 +13362,13 @@
       </c>
       <c r="H223" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I223" s="11" t="n"/>
       <c r="J223" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
+          <t>Cerrada por Catalina Pescio (pruebas y documentación del módulo) — 29-09-2026.</t>
         </is>
       </c>
     </row>
@@ -13858,13 +13888,13 @@
       </c>
       <c r="H234" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -13904,13 +13934,13 @@
       </c>
       <c r="H235" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I235" s="11" t="n"/>
       <c r="J235" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14314,13 +14344,13 @@
       </c>
       <c r="H244" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I244" s="11" t="n"/>
       <c r="J244" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14360,13 +14390,13 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I245" s="11" t="n"/>
       <c r="J245" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
+          <t>Ejecutada/cerrada por Catalina Pescio en el cierre del módulo (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14406,13 +14436,13 @@
       </c>
       <c r="H246" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I246" s="11" t="n"/>
       <c r="J246" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14452,13 +14482,13 @@
       </c>
       <c r="H247" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I247" s="11" t="n"/>
       <c r="J247" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14498,13 +14528,13 @@
       </c>
       <c r="H248" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I248" s="11" t="n"/>
       <c r="J248" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14544,13 +14574,13 @@
       </c>
       <c r="H249" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I249" s="11" t="n"/>
       <c r="J249" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14590,13 +14620,13 @@
       </c>
       <c r="H250" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I250" s="11" t="n"/>
       <c r="J250" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14636,13 +14666,13 @@
       </c>
       <c r="H251" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I251" s="11" t="n"/>
       <c r="J251" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14682,13 +14712,13 @@
       </c>
       <c r="H252" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -14728,13 +14758,13 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I253" s="11" t="n"/>
       <c r="J253" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (29-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (29-09-2026).</t>
         </is>
       </c>
     </row>
@@ -15234,13 +15264,13 @@
       </c>
       <c r="H264" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I264" s="11" t="n"/>
       <c r="J264" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -15280,13 +15310,13 @@
       </c>
       <c r="H265" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I265" s="11" t="n"/>
       <c r="J265" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -15878,13 +15908,13 @@
       </c>
       <c r="H278" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I278" s="11" t="n"/>
       <c r="J278" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -15924,13 +15954,13 @@
       </c>
       <c r="H279" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminada</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="I279" s="11" t="n"/>
       <c r="J279" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerrada por Catalina Pescio (24-09-2026).</t>
+          <t>Cerrada por Catalina Pescio (24-09-2026).</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16636,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16637,7 +16667,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16699,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16730,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17655,7 @@
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17656,7 +17686,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17718,7 @@
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18566,7 +18596,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18616,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18606,7 +18636,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18626,7 +18656,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18676,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18666,7 +18696,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18716,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18706,7 +18736,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18726,10 +18756,11 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="20" t="inlineStr">
         <is>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S4.xlsx
@@ -1965,7 +1965,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>Mantenedor de umbrales/acciones construido por Catalina: SP SEL/INS/UPD/DEL_CHECKLIST_ITEM_VALIDACION (BD/307), pantallas ChecklistItemValidacion(s) + controller/modelo, permisos/menú (BD/308). Pruebas (CA-1: 84-&gt;crítica; CA-2/3/4 definición+runtime) y documentación cerradas (29-09-2026). Pendiente solo la validación funcional con la PO (T-4137).</t>
+          <t>Mantenedor de umbrales/acciones construido por Catalina: SP SEL/INS/UPD/DEL_CHECKLIST_ITEM_VALIDACION (BD/307), pantallas ChecklistItemValidacion(s) + controller/modelo, permisos/menú (BD/308). Pruebas (CA-1: 84-&gt;crítica; CA-2/3/4 definición+runtime) y documentación cerradas (29-09-2026). Validación funcional con la PO conforme (T-4137).</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I101" s="11" t="n"/>
+      <c r="I101" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7765,7 +7767,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I102" s="11" t="n"/>
+      <c r="I102" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7811,7 +7815,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I103" s="11" t="n"/>
+      <c r="I103" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J103" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7857,7 +7863,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I104" s="11" t="n"/>
+      <c r="I104" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7903,7 +7911,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I105" s="11" t="n"/>
+      <c r="I105" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J105" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7949,7 +7959,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I106" s="11" t="n"/>
+      <c r="I106" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J106" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -7995,7 +8007,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I107" s="11" t="n"/>
+      <c r="I107" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J107" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -8041,7 +8055,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I108" s="11" t="n"/>
+      <c r="I108" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -8087,7 +8103,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I109" s="11" t="n"/>
+      <c r="I109" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J109" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -8133,7 +8151,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I110" s="11" t="n"/>
+      <c r="I110" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -8179,7 +8199,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I111" s="11" t="n"/>
+      <c r="I111" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J111" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -8225,7 +8247,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I112" s="11" t="n"/>
+      <c r="I112" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14439,7 +14463,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I246" s="11" t="n"/>
+      <c r="I246" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J246" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14485,7 +14511,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I247" s="11" t="n"/>
+      <c r="I247" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J247" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14531,7 +14559,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I248" s="11" t="n"/>
+      <c r="I248" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J248" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14577,7 +14607,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I249" s="11" t="n"/>
+      <c r="I249" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J249" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14623,7 +14655,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I250" s="11" t="n"/>
+      <c r="I250" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J250" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14669,7 +14703,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I251" s="11" t="n"/>
+      <c r="I251" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J251" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14715,7 +14751,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I252" s="11" t="n"/>
+      <c r="I252" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J252" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -14761,7 +14799,9 @@
           <t>Terminada</t>
         </is>
       </c>
-      <c r="I253" s="11" t="n"/>
+      <c r="I253" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J253" s="12" t="inlineStr">
         <is>
           <t>Cerrada por Catalina Pescio (29-09-2026).</t>
@@ -17110,7 +17150,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17182,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17214,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -17207,7 +17247,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18348,7 +18388,7 @@
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18420,7 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18800,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="15" customHeight="1" s="19">
       <c r="A16" s="20" t="inlineStr">
         <is>
